--- a/static/Files/Template - GPCRome wheel - Numeric.xlsx
+++ b/static/Files/Template - GPCRome wheel - Numeric.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28730"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dcs839\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dcs839\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{987F555E-97C4-41A6-AA31-F7DCB8666E14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEFDA312-0C46-4C43-88B9-7E158452B5A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2329,7 +2329,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -2374,34 +2374,10 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
       <top/>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -2421,7 +2397,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2432,7 +2408,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -2440,22 +2416,14 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2472,28 +2440,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="20">
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-      <protection locked="1" hidden="0"/>
-    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -2688,6 +2634,28 @@
       </border>
     </dxf>
     <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -2823,11 +2791,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{5AC62491-8126-441A-8A95-20F4467A898A}" name="GPCRomeTable" displayName="GPCRomeTable" ref="A1:C399" totalsRowShown="0" headerRowDxfId="19" dataDxfId="17" headerRowBorderDxfId="18" tableBorderDxfId="16" totalsRowBorderDxfId="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{5AC62491-8126-441A-8A95-20F4467A898A}" name="GPCRomeTable" displayName="GPCRomeTable" ref="A1:C398" totalsRowShown="0" headerRowDxfId="19" dataDxfId="17" headerRowBorderDxfId="18" tableBorderDxfId="16" totalsRowBorderDxfId="15">
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{020B8C2E-97A4-4923-ACC4-D91BEC1F20DC}" name="GPCRs_x000a_(Gene or Uniprot name)" dataDxfId="14"/>
     <tableColumn id="2" xr3:uid="{737746CB-0567-4FA5-B974-F7E7A483801B}" name="Add numbers_x000a_(Visualized as Gradient of one or two colors)" dataDxfId="13"/>
-    <tableColumn id="4" xr3:uid="{BDC466DD-799A-4645-AD5B-861D19910E63}" name="Info / error" dataDxfId="0">
+    <tableColumn id="4" xr3:uid="{BDC466DD-799A-4645-AD5B-861D19910E63}" name="Info / error" dataDxfId="12">
       <calculatedColumnFormula>IF(A2="",
     IF(B2&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -2850,17 +2818,17 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B10A972E-CF63-4BA4-BEA4-CC0EA53E3C69}" name="ReceptorData" displayName="ReceptorData" ref="A1:E398" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B10A972E-CF63-4BA4-BEA4-CC0EA53E3C69}" name="ReceptorData" displayName="ReceptorData" ref="A1:E398" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
   <autoFilter ref="A1:E398" xr:uid="{B10A972E-CF63-4BA4-BEA4-CC0EA53E3C69}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E398">
     <sortCondition ref="E1:E398"/>
   </sortState>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{D15B2A36-6DAD-4B74-953C-81C46617F40E}" name="GPCRs_x000a_(UniProt)" dataDxfId="10"/>
-    <tableColumn id="9" xr3:uid="{3D563267-CF61-4CF1-A6D5-550F4368E187}" name="GPCRs_x000a_(Gene name)" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{E125A5E4-5FE4-4EF1-8300-EBB2B09FE20A}" name="Receptor family" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{5D4D1D7F-4883-4967-A90A-ED5DAC9C412F}" name="Ligand type" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{492927CC-2139-456C-8D6F-16C543F2D5E6}" name="Class" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{D15B2A36-6DAD-4B74-953C-81C46617F40E}" name="GPCRs_x000a_(UniProt)" dataDxfId="9"/>
+    <tableColumn id="9" xr3:uid="{3D563267-CF61-4CF1-A6D5-550F4368E187}" name="GPCRs_x000a_(Gene name)" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{E125A5E4-5FE4-4EF1-8300-EBB2B09FE20A}" name="Receptor family" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{5D4D1D7F-4883-4967-A90A-ED5DAC9C412F}" name="Ligand type" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{492927CC-2139-456C-8D6F-16C543F2D5E6}" name="Class" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3129,7 +3097,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E552C984-CB4E-45B6-83C9-925F4E5D96AD}">
-  <dimension ref="A1:C399"/>
+  <dimension ref="A1:C398"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="31.08984375" style="1" customWidth="1"/>
@@ -3138,20 +3106,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="70" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="11" t="s">
         <v>723</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="7" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15" thickTop="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="10" t="str">
+      <c r="B2" s="6"/>
+      <c r="C2" s="8" t="str">
         <f>IF(A2="",
     IF(B2&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -3173,7 +3141,7 @@
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
       <c r="B3" s="5"/>
-      <c r="C3" s="10" t="str">
+      <c r="C3" s="8" t="str">
         <f>IF(A3="",
     IF(B3&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -3195,7 +3163,7 @@
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="3"/>
       <c r="B4" s="5"/>
-      <c r="C4" s="10" t="str">
+      <c r="C4" s="8" t="str">
         <f>IF(A4="",
     IF(B4&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -3217,7 +3185,7 @@
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3"/>
       <c r="B5" s="5"/>
-      <c r="C5" s="10" t="str">
+      <c r="C5" s="8" t="str">
         <f>IF(A5="",
     IF(B5&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -3239,7 +3207,7 @@
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3"/>
       <c r="B6" s="5"/>
-      <c r="C6" s="10" t="str">
+      <c r="C6" s="8" t="str">
         <f>IF(A6="",
     IF(B6&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -3261,7 +3229,7 @@
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3"/>
       <c r="B7" s="5"/>
-      <c r="C7" s="10" t="str">
+      <c r="C7" s="8" t="str">
         <f>IF(A7="",
     IF(B7&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -3283,7 +3251,7 @@
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3"/>
       <c r="B8" s="5"/>
-      <c r="C8" s="10" t="str">
+      <c r="C8" s="8" t="str">
         <f>IF(A8="",
     IF(B8&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -3305,7 +3273,7 @@
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3"/>
       <c r="B9" s="5"/>
-      <c r="C9" s="10" t="str">
+      <c r="C9" s="8" t="str">
         <f>IF(A9="",
     IF(B9&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -3326,8 +3294,8 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="10" t="str">
+      <c r="B10" s="6"/>
+      <c r="C10" s="8" t="str">
         <f>IF(A10="",
     IF(B10&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -3349,7 +3317,7 @@
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="3"/>
       <c r="B11" s="5"/>
-      <c r="C11" s="10" t="str">
+      <c r="C11" s="8" t="str">
         <f>IF(A11="",
     IF(B11&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -3371,7 +3339,7 @@
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="3"/>
       <c r="B12" s="5"/>
-      <c r="C12" s="10" t="str">
+      <c r="C12" s="8" t="str">
         <f>IF(A12="",
     IF(B12&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -3393,7 +3361,7 @@
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="3"/>
       <c r="B13" s="5"/>
-      <c r="C13" s="10" t="str">
+      <c r="C13" s="8" t="str">
         <f>IF(A13="",
     IF(B13&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -3415,7 +3383,7 @@
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="3"/>
       <c r="B14" s="5"/>
-      <c r="C14" s="10" t="str">
+      <c r="C14" s="8" t="str">
         <f>IF(A14="",
     IF(B14&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -3437,7 +3405,7 @@
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="3"/>
       <c r="B15" s="5"/>
-      <c r="C15" s="10" t="str">
+      <c r="C15" s="8" t="str">
         <f>IF(A15="",
     IF(B15&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -3459,7 +3427,7 @@
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="3"/>
       <c r="B16" s="5"/>
-      <c r="C16" s="10" t="str">
+      <c r="C16" s="8" t="str">
         <f>IF(A16="",
     IF(B16&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -3481,7 +3449,7 @@
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="3"/>
       <c r="B17" s="5"/>
-      <c r="C17" s="10" t="str">
+      <c r="C17" s="8" t="str">
         <f>IF(A17="",
     IF(B17&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -3502,8 +3470,8 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="3"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="10" t="str">
+      <c r="B18" s="6"/>
+      <c r="C18" s="8" t="str">
         <f>IF(A18="",
     IF(B18&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -3525,7 +3493,7 @@
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="3"/>
       <c r="B19" s="5"/>
-      <c r="C19" s="10" t="str">
+      <c r="C19" s="8" t="str">
         <f>IF(A19="",
     IF(B19&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -3547,7 +3515,7 @@
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="3"/>
       <c r="B20" s="5"/>
-      <c r="C20" s="10" t="str">
+      <c r="C20" s="8" t="str">
         <f>IF(A20="",
     IF(B20&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -3569,7 +3537,7 @@
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="3"/>
       <c r="B21" s="5"/>
-      <c r="C21" s="10" t="str">
+      <c r="C21" s="8" t="str">
         <f>IF(A21="",
     IF(B21&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -3591,7 +3559,7 @@
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="3"/>
       <c r="B22" s="5"/>
-      <c r="C22" s="10" t="str">
+      <c r="C22" s="8" t="str">
         <f>IF(A22="",
     IF(B22&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -3613,7 +3581,7 @@
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" s="3"/>
       <c r="B23" s="5"/>
-      <c r="C23" s="10" t="str">
+      <c r="C23" s="8" t="str">
         <f>IF(A23="",
     IF(B23&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -3635,7 +3603,7 @@
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" s="3"/>
       <c r="B24" s="5"/>
-      <c r="C24" s="10" t="str">
+      <c r="C24" s="8" t="str">
         <f>IF(A24="",
     IF(B24&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -3657,7 +3625,7 @@
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="3"/>
       <c r="B25" s="5"/>
-      <c r="C25" s="10" t="str">
+      <c r="C25" s="8" t="str">
         <f>IF(A25="",
     IF(B25&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -3678,8 +3646,8 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="3"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="10" t="str">
+      <c r="B26" s="6"/>
+      <c r="C26" s="8" t="str">
         <f>IF(A26="",
     IF(B26&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -3701,7 +3669,7 @@
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" s="3"/>
       <c r="B27" s="5"/>
-      <c r="C27" s="10" t="str">
+      <c r="C27" s="8" t="str">
         <f>IF(A27="",
     IF(B27&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -3723,7 +3691,7 @@
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" s="3"/>
       <c r="B28" s="5"/>
-      <c r="C28" s="10" t="str">
+      <c r="C28" s="8" t="str">
         <f>IF(A28="",
     IF(B28&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -3745,7 +3713,7 @@
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" s="3"/>
       <c r="B29" s="5"/>
-      <c r="C29" s="10" t="str">
+      <c r="C29" s="8" t="str">
         <f>IF(A29="",
     IF(B29&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -3767,7 +3735,7 @@
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="3"/>
       <c r="B30" s="5"/>
-      <c r="C30" s="10" t="str">
+      <c r="C30" s="8" t="str">
         <f>IF(A30="",
     IF(B30&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -3789,7 +3757,7 @@
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" s="3"/>
       <c r="B31" s="5"/>
-      <c r="C31" s="10" t="str">
+      <c r="C31" s="8" t="str">
         <f>IF(A31="",
     IF(B31&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -3811,7 +3779,7 @@
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" s="3"/>
       <c r="B32" s="5"/>
-      <c r="C32" s="10" t="str">
+      <c r="C32" s="8" t="str">
         <f>IF(A32="",
     IF(B32&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -3833,7 +3801,7 @@
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" s="3"/>
       <c r="B33" s="5"/>
-      <c r="C33" s="10" t="str">
+      <c r="C33" s="8" t="str">
         <f>IF(A33="",
     IF(B33&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -3855,7 +3823,7 @@
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" s="4"/>
       <c r="B34" s="5"/>
-      <c r="C34" s="10" t="str">
+      <c r="C34" s="8" t="str">
         <f>IF(A34="",
     IF(B34&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -3877,7 +3845,7 @@
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" s="4"/>
       <c r="B35" s="5"/>
-      <c r="C35" s="10" t="str">
+      <c r="C35" s="8" t="str">
         <f>IF(A35="",
     IF(B35&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -3899,7 +3867,7 @@
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" s="4"/>
       <c r="B36" s="5"/>
-      <c r="C36" s="10" t="str">
+      <c r="C36" s="8" t="str">
         <f>IF(A36="",
     IF(B36&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -3921,7 +3889,7 @@
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" s="4"/>
       <c r="B37" s="5"/>
-      <c r="C37" s="10" t="str">
+      <c r="C37" s="8" t="str">
         <f>IF(A37="",
     IF(B37&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -3943,7 +3911,7 @@
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" s="4"/>
       <c r="B38" s="5"/>
-      <c r="C38" s="10" t="str">
+      <c r="C38" s="8" t="str">
         <f>IF(A38="",
     IF(B38&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -3965,7 +3933,7 @@
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" s="4"/>
       <c r="B39" s="5"/>
-      <c r="C39" s="10" t="str">
+      <c r="C39" s="8" t="str">
         <f>IF(A39="",
     IF(B39&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -3987,7 +3955,7 @@
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" s="4"/>
       <c r="B40" s="5"/>
-      <c r="C40" s="10" t="str">
+      <c r="C40" s="8" t="str">
         <f>IF(A40="",
     IF(B40&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -4009,7 +3977,7 @@
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" s="4"/>
       <c r="B41" s="5"/>
-      <c r="C41" s="10" t="str">
+      <c r="C41" s="8" t="str">
         <f>IF(A41="",
     IF(B41&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -4031,7 +3999,7 @@
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" s="4"/>
       <c r="B42" s="5"/>
-      <c r="C42" s="10" t="str">
+      <c r="C42" s="8" t="str">
         <f>IF(A42="",
     IF(B42&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -4053,7 +4021,7 @@
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" s="4"/>
       <c r="B43" s="5"/>
-      <c r="C43" s="10" t="str">
+      <c r="C43" s="8" t="str">
         <f>IF(A43="",
     IF(B43&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -4075,7 +4043,7 @@
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" s="4"/>
       <c r="B44" s="5"/>
-      <c r="C44" s="10" t="str">
+      <c r="C44" s="8" t="str">
         <f>IF(A44="",
     IF(B44&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -4097,7 +4065,7 @@
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" s="4"/>
       <c r="B45" s="5"/>
-      <c r="C45" s="10" t="str">
+      <c r="C45" s="8" t="str">
         <f>IF(A45="",
     IF(B45&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -4119,7 +4087,7 @@
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" s="4"/>
       <c r="B46" s="5"/>
-      <c r="C46" s="10" t="str">
+      <c r="C46" s="8" t="str">
         <f>IF(A46="",
     IF(B46&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -4141,7 +4109,7 @@
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" s="4"/>
       <c r="B47" s="5"/>
-      <c r="C47" s="10" t="str">
+      <c r="C47" s="8" t="str">
         <f>IF(A47="",
     IF(B47&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -4163,7 +4131,7 @@
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" s="4"/>
       <c r="B48" s="5"/>
-      <c r="C48" s="10" t="str">
+      <c r="C48" s="8" t="str">
         <f>IF(A48="",
     IF(B48&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -4185,7 +4153,7 @@
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" s="4"/>
       <c r="B49" s="5"/>
-      <c r="C49" s="10" t="str">
+      <c r="C49" s="8" t="str">
         <f>IF(A49="",
     IF(B49&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -4207,7 +4175,7 @@
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" s="4"/>
       <c r="B50" s="5"/>
-      <c r="C50" s="10" t="str">
+      <c r="C50" s="8" t="str">
         <f>IF(A50="",
     IF(B50&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -4229,7 +4197,7 @@
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" s="4"/>
       <c r="B51" s="5"/>
-      <c r="C51" s="10" t="str">
+      <c r="C51" s="8" t="str">
         <f>IF(A51="",
     IF(B51&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -4251,7 +4219,7 @@
     <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" s="4"/>
       <c r="B52" s="5"/>
-      <c r="C52" s="10" t="str">
+      <c r="C52" s="8" t="str">
         <f>IF(A52="",
     IF(B52&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -4273,7 +4241,7 @@
     <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" s="4"/>
       <c r="B53" s="5"/>
-      <c r="C53" s="10" t="str">
+      <c r="C53" s="8" t="str">
         <f>IF(A53="",
     IF(B53&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -4295,7 +4263,7 @@
     <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" s="4"/>
       <c r="B54" s="5"/>
-      <c r="C54" s="10" t="str">
+      <c r="C54" s="8" t="str">
         <f>IF(A54="",
     IF(B54&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -4317,7 +4285,7 @@
     <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" s="4"/>
       <c r="B55" s="5"/>
-      <c r="C55" s="10" t="str">
+      <c r="C55" s="8" t="str">
         <f>IF(A55="",
     IF(B55&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -4339,7 +4307,7 @@
     <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" s="4"/>
       <c r="B56" s="5"/>
-      <c r="C56" s="10" t="str">
+      <c r="C56" s="8" t="str">
         <f>IF(A56="",
     IF(B56&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -4361,7 +4329,7 @@
     <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" s="4"/>
       <c r="B57" s="5"/>
-      <c r="C57" s="10" t="str">
+      <c r="C57" s="8" t="str">
         <f>IF(A57="",
     IF(B57&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -4383,7 +4351,7 @@
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" s="4"/>
       <c r="B58" s="5"/>
-      <c r="C58" s="10" t="str">
+      <c r="C58" s="8" t="str">
         <f>IF(A58="",
     IF(B58&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -4405,7 +4373,7 @@
     <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" s="4"/>
       <c r="B59" s="5"/>
-      <c r="C59" s="10" t="str">
+      <c r="C59" s="8" t="str">
         <f>IF(A59="",
     IF(B59&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -4427,7 +4395,7 @@
     <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" s="4"/>
       <c r="B60" s="5"/>
-      <c r="C60" s="10" t="str">
+      <c r="C60" s="8" t="str">
         <f>IF(A60="",
     IF(B60&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -4449,7 +4417,7 @@
     <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" s="4"/>
       <c r="B61" s="5"/>
-      <c r="C61" s="10" t="str">
+      <c r="C61" s="8" t="str">
         <f>IF(A61="",
     IF(B61&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -4471,7 +4439,7 @@
     <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" s="4"/>
       <c r="B62" s="5"/>
-      <c r="C62" s="10" t="str">
+      <c r="C62" s="8" t="str">
         <f>IF(A62="",
     IF(B62&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -4493,7 +4461,7 @@
     <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" s="4"/>
       <c r="B63" s="5"/>
-      <c r="C63" s="10" t="str">
+      <c r="C63" s="8" t="str">
         <f>IF(A63="",
     IF(B63&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -4515,7 +4483,7 @@
     <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" s="4"/>
       <c r="B64" s="5"/>
-      <c r="C64" s="10" t="str">
+      <c r="C64" s="8" t="str">
         <f>IF(A64="",
     IF(B64&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -4537,7 +4505,7 @@
     <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" s="4"/>
       <c r="B65" s="5"/>
-      <c r="C65" s="10" t="str">
+      <c r="C65" s="8" t="str">
         <f>IF(A65="",
     IF(B65&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -4559,7 +4527,7 @@
     <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" s="4"/>
       <c r="B66" s="5"/>
-      <c r="C66" s="10" t="str">
+      <c r="C66" s="8" t="str">
         <f>IF(A66="",
     IF(B66&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -4581,7 +4549,7 @@
     <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" s="4"/>
       <c r="B67" s="5"/>
-      <c r="C67" s="10" t="str">
+      <c r="C67" s="8" t="str">
         <f>IF(A67="",
     IF(B67&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -4603,7 +4571,7 @@
     <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" s="4"/>
       <c r="B68" s="5"/>
-      <c r="C68" s="10" t="str">
+      <c r="C68" s="8" t="str">
         <f>IF(A68="",
     IF(B68&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -4625,7 +4593,7 @@
     <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" s="4"/>
       <c r="B69" s="5"/>
-      <c r="C69" s="10" t="str">
+      <c r="C69" s="8" t="str">
         <f>IF(A69="",
     IF(B69&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -4647,7 +4615,7 @@
     <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" s="4"/>
       <c r="B70" s="5"/>
-      <c r="C70" s="10" t="str">
+      <c r="C70" s="8" t="str">
         <f>IF(A70="",
     IF(B70&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -4669,7 +4637,7 @@
     <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" s="4"/>
       <c r="B71" s="5"/>
-      <c r="C71" s="10" t="str">
+      <c r="C71" s="8" t="str">
         <f>IF(A71="",
     IF(B71&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -4691,7 +4659,7 @@
     <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72" s="4"/>
       <c r="B72" s="5"/>
-      <c r="C72" s="10" t="str">
+      <c r="C72" s="8" t="str">
         <f>IF(A72="",
     IF(B72&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -4713,7 +4681,7 @@
     <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73" s="4"/>
       <c r="B73" s="5"/>
-      <c r="C73" s="10" t="str">
+      <c r="C73" s="8" t="str">
         <f>IF(A73="",
     IF(B73&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -4735,7 +4703,7 @@
     <row r="74" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A74" s="4"/>
       <c r="B74" s="5"/>
-      <c r="C74" s="10" t="str">
+      <c r="C74" s="8" t="str">
         <f>IF(A74="",
     IF(B74&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -4757,7 +4725,7 @@
     <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75" s="4"/>
       <c r="B75" s="5"/>
-      <c r="C75" s="10" t="str">
+      <c r="C75" s="8" t="str">
         <f>IF(A75="",
     IF(B75&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -4779,7 +4747,7 @@
     <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A76" s="4"/>
       <c r="B76" s="5"/>
-      <c r="C76" s="10" t="str">
+      <c r="C76" s="8" t="str">
         <f>IF(A76="",
     IF(B76&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -4801,7 +4769,7 @@
     <row r="77" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A77" s="4"/>
       <c r="B77" s="5"/>
-      <c r="C77" s="10" t="str">
+      <c r="C77" s="8" t="str">
         <f>IF(A77="",
     IF(B77&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -4823,7 +4791,7 @@
     <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A78" s="4"/>
       <c r="B78" s="5"/>
-      <c r="C78" s="10" t="str">
+      <c r="C78" s="8" t="str">
         <f>IF(A78="",
     IF(B78&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -4845,7 +4813,7 @@
     <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A79" s="4"/>
       <c r="B79" s="5"/>
-      <c r="C79" s="10" t="str">
+      <c r="C79" s="8" t="str">
         <f>IF(A79="",
     IF(B79&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -4867,7 +4835,7 @@
     <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80" s="4"/>
       <c r="B80" s="5"/>
-      <c r="C80" s="10" t="str">
+      <c r="C80" s="8" t="str">
         <f>IF(A80="",
     IF(B80&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -4889,7 +4857,7 @@
     <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A81" s="4"/>
       <c r="B81" s="5"/>
-      <c r="C81" s="10" t="str">
+      <c r="C81" s="8" t="str">
         <f>IF(A81="",
     IF(B81&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -4911,7 +4879,7 @@
     <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82" s="4"/>
       <c r="B82" s="5"/>
-      <c r="C82" s="10" t="str">
+      <c r="C82" s="8" t="str">
         <f>IF(A82="",
     IF(B82&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -4933,7 +4901,7 @@
     <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83" s="4"/>
       <c r="B83" s="5"/>
-      <c r="C83" s="10" t="str">
+      <c r="C83" s="8" t="str">
         <f>IF(A83="",
     IF(B83&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -4955,7 +4923,7 @@
     <row r="84" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A84" s="4"/>
       <c r="B84" s="5"/>
-      <c r="C84" s="10" t="str">
+      <c r="C84" s="8" t="str">
         <f>IF(A84="",
     IF(B84&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -4977,7 +4945,7 @@
     <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85" s="4"/>
       <c r="B85" s="5"/>
-      <c r="C85" s="10" t="str">
+      <c r="C85" s="8" t="str">
         <f>IF(A85="",
     IF(B85&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -4999,7 +4967,7 @@
     <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86" s="4"/>
       <c r="B86" s="5"/>
-      <c r="C86" s="10" t="str">
+      <c r="C86" s="8" t="str">
         <f>IF(A86="",
     IF(B86&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -5021,7 +4989,7 @@
     <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A87" s="4"/>
       <c r="B87" s="5"/>
-      <c r="C87" s="10" t="str">
+      <c r="C87" s="8" t="str">
         <f>IF(A87="",
     IF(B87&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -5043,7 +5011,7 @@
     <row r="88" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A88" s="4"/>
       <c r="B88" s="5"/>
-      <c r="C88" s="10" t="str">
+      <c r="C88" s="8" t="str">
         <f>IF(A88="",
     IF(B88&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -5065,7 +5033,7 @@
     <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89" s="4"/>
       <c r="B89" s="5"/>
-      <c r="C89" s="10" t="str">
+      <c r="C89" s="8" t="str">
         <f>IF(A89="",
     IF(B89&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -5087,7 +5055,7 @@
     <row r="90" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A90" s="4"/>
       <c r="B90" s="5"/>
-      <c r="C90" s="10" t="str">
+      <c r="C90" s="8" t="str">
         <f>IF(A90="",
     IF(B90&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -5109,7 +5077,7 @@
     <row r="91" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A91" s="4"/>
       <c r="B91" s="5"/>
-      <c r="C91" s="10" t="str">
+      <c r="C91" s="8" t="str">
         <f>IF(A91="",
     IF(B91&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -5131,7 +5099,7 @@
     <row r="92" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A92" s="4"/>
       <c r="B92" s="5"/>
-      <c r="C92" s="10" t="str">
+      <c r="C92" s="8" t="str">
         <f>IF(A92="",
     IF(B92&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -5153,7 +5121,7 @@
     <row r="93" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A93" s="4"/>
       <c r="B93" s="5"/>
-      <c r="C93" s="10" t="str">
+      <c r="C93" s="8" t="str">
         <f>IF(A93="",
     IF(B93&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -5175,7 +5143,7 @@
     <row r="94" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A94" s="4"/>
       <c r="B94" s="5"/>
-      <c r="C94" s="10" t="str">
+      <c r="C94" s="8" t="str">
         <f>IF(A94="",
     IF(B94&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -5197,7 +5165,7 @@
     <row r="95" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A95" s="4"/>
       <c r="B95" s="5"/>
-      <c r="C95" s="10" t="str">
+      <c r="C95" s="8" t="str">
         <f>IF(A95="",
     IF(B95&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -5219,7 +5187,7 @@
     <row r="96" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A96" s="4"/>
       <c r="B96" s="5"/>
-      <c r="C96" s="10" t="str">
+      <c r="C96" s="8" t="str">
         <f>IF(A96="",
     IF(B96&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -5241,7 +5209,7 @@
     <row r="97" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A97" s="4"/>
       <c r="B97" s="5"/>
-      <c r="C97" s="10" t="str">
+      <c r="C97" s="8" t="str">
         <f>IF(A97="",
     IF(B97&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -5263,7 +5231,7 @@
     <row r="98" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A98" s="4"/>
       <c r="B98" s="5"/>
-      <c r="C98" s="10" t="str">
+      <c r="C98" s="8" t="str">
         <f>IF(A98="",
     IF(B98&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -5285,7 +5253,7 @@
     <row r="99" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A99" s="4"/>
       <c r="B99" s="5"/>
-      <c r="C99" s="10" t="str">
+      <c r="C99" s="8" t="str">
         <f>IF(A99="",
     IF(B99&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -5307,7 +5275,7 @@
     <row r="100" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A100" s="4"/>
       <c r="B100" s="5"/>
-      <c r="C100" s="10" t="str">
+      <c r="C100" s="8" t="str">
         <f>IF(A100="",
     IF(B100&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -5329,7 +5297,7 @@
     <row r="101" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A101" s="4"/>
       <c r="B101" s="5"/>
-      <c r="C101" s="10" t="str">
+      <c r="C101" s="8" t="str">
         <f>IF(A101="",
     IF(B101&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -5351,7 +5319,7 @@
     <row r="102" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A102" s="4"/>
       <c r="B102" s="5"/>
-      <c r="C102" s="10" t="str">
+      <c r="C102" s="8" t="str">
         <f>IF(A102="",
     IF(B102&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -5373,7 +5341,7 @@
     <row r="103" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A103" s="4"/>
       <c r="B103" s="5"/>
-      <c r="C103" s="10" t="str">
+      <c r="C103" s="8" t="str">
         <f>IF(A103="",
     IF(B103&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -5395,7 +5363,7 @@
     <row r="104" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A104" s="4"/>
       <c r="B104" s="5"/>
-      <c r="C104" s="10" t="str">
+      <c r="C104" s="8" t="str">
         <f>IF(A104="",
     IF(B104&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -5417,7 +5385,7 @@
     <row r="105" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A105" s="4"/>
       <c r="B105" s="5"/>
-      <c r="C105" s="10" t="str">
+      <c r="C105" s="8" t="str">
         <f>IF(A105="",
     IF(B105&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -5439,7 +5407,7 @@
     <row r="106" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A106" s="4"/>
       <c r="B106" s="5"/>
-      <c r="C106" s="10" t="str">
+      <c r="C106" s="8" t="str">
         <f>IF(A106="",
     IF(B106&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -5461,7 +5429,7 @@
     <row r="107" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A107" s="4"/>
       <c r="B107" s="5"/>
-      <c r="C107" s="10" t="str">
+      <c r="C107" s="8" t="str">
         <f>IF(A107="",
     IF(B107&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -5483,7 +5451,7 @@
     <row r="108" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A108" s="4"/>
       <c r="B108" s="5"/>
-      <c r="C108" s="10" t="str">
+      <c r="C108" s="8" t="str">
         <f>IF(A108="",
     IF(B108&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -5505,7 +5473,7 @@
     <row r="109" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A109" s="4"/>
       <c r="B109" s="5"/>
-      <c r="C109" s="10" t="str">
+      <c r="C109" s="8" t="str">
         <f>IF(A109="",
     IF(B109&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -5527,7 +5495,7 @@
     <row r="110" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A110" s="4"/>
       <c r="B110" s="5"/>
-      <c r="C110" s="10" t="str">
+      <c r="C110" s="8" t="str">
         <f>IF(A110="",
     IF(B110&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -5549,7 +5517,7 @@
     <row r="111" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A111" s="4"/>
       <c r="B111" s="5"/>
-      <c r="C111" s="10" t="str">
+      <c r="C111" s="8" t="str">
         <f>IF(A111="",
     IF(B111&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -5571,7 +5539,7 @@
     <row r="112" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A112" s="4"/>
       <c r="B112" s="5"/>
-      <c r="C112" s="10" t="str">
+      <c r="C112" s="8" t="str">
         <f>IF(A112="",
     IF(B112&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -5593,7 +5561,7 @@
     <row r="113" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A113" s="4"/>
       <c r="B113" s="5"/>
-      <c r="C113" s="10" t="str">
+      <c r="C113" s="8" t="str">
         <f>IF(A113="",
     IF(B113&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -5615,7 +5583,7 @@
     <row r="114" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A114" s="4"/>
       <c r="B114" s="5"/>
-      <c r="C114" s="10" t="str">
+      <c r="C114" s="8" t="str">
         <f>IF(A114="",
     IF(B114&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -5637,7 +5605,7 @@
     <row r="115" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A115" s="4"/>
       <c r="B115" s="5"/>
-      <c r="C115" s="10" t="str">
+      <c r="C115" s="8" t="str">
         <f>IF(A115="",
     IF(B115&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -5659,7 +5627,7 @@
     <row r="116" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A116" s="4"/>
       <c r="B116" s="5"/>
-      <c r="C116" s="10" t="str">
+      <c r="C116" s="8" t="str">
         <f>IF(A116="",
     IF(B116&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -5681,7 +5649,7 @@
     <row r="117" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A117" s="4"/>
       <c r="B117" s="5"/>
-      <c r="C117" s="10" t="str">
+      <c r="C117" s="8" t="str">
         <f>IF(A117="",
     IF(B117&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -5703,7 +5671,7 @@
     <row r="118" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A118" s="4"/>
       <c r="B118" s="5"/>
-      <c r="C118" s="10" t="str">
+      <c r="C118" s="8" t="str">
         <f>IF(A118="",
     IF(B118&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -5725,7 +5693,7 @@
     <row r="119" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A119" s="4"/>
       <c r="B119" s="5"/>
-      <c r="C119" s="10" t="str">
+      <c r="C119" s="8" t="str">
         <f>IF(A119="",
     IF(B119&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -5747,7 +5715,7 @@
     <row r="120" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A120" s="4"/>
       <c r="B120" s="5"/>
-      <c r="C120" s="10" t="str">
+      <c r="C120" s="8" t="str">
         <f>IF(A120="",
     IF(B120&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -5769,7 +5737,7 @@
     <row r="121" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A121" s="4"/>
       <c r="B121" s="5"/>
-      <c r="C121" s="10" t="str">
+      <c r="C121" s="8" t="str">
         <f>IF(A121="",
     IF(B121&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -5791,7 +5759,7 @@
     <row r="122" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A122" s="4"/>
       <c r="B122" s="5"/>
-      <c r="C122" s="10" t="str">
+      <c r="C122" s="8" t="str">
         <f>IF(A122="",
     IF(B122&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -5813,7 +5781,7 @@
     <row r="123" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A123" s="4"/>
       <c r="B123" s="5"/>
-      <c r="C123" s="10" t="str">
+      <c r="C123" s="8" t="str">
         <f>IF(A123="",
     IF(B123&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -5835,7 +5803,7 @@
     <row r="124" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A124" s="4"/>
       <c r="B124" s="5"/>
-      <c r="C124" s="10" t="str">
+      <c r="C124" s="8" t="str">
         <f>IF(A124="",
     IF(B124&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -5857,7 +5825,7 @@
     <row r="125" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A125" s="4"/>
       <c r="B125" s="5"/>
-      <c r="C125" s="10" t="str">
+      <c r="C125" s="8" t="str">
         <f>IF(A125="",
     IF(B125&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -5879,7 +5847,7 @@
     <row r="126" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A126" s="4"/>
       <c r="B126" s="5"/>
-      <c r="C126" s="10" t="str">
+      <c r="C126" s="8" t="str">
         <f>IF(A126="",
     IF(B126&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -5901,7 +5869,7 @@
     <row r="127" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A127" s="4"/>
       <c r="B127" s="5"/>
-      <c r="C127" s="10" t="str">
+      <c r="C127" s="8" t="str">
         <f>IF(A127="",
     IF(B127&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -5923,7 +5891,7 @@
     <row r="128" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A128" s="4"/>
       <c r="B128" s="5"/>
-      <c r="C128" s="10" t="str">
+      <c r="C128" s="8" t="str">
         <f>IF(A128="",
     IF(B128&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -5945,7 +5913,7 @@
     <row r="129" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A129" s="4"/>
       <c r="B129" s="5"/>
-      <c r="C129" s="10" t="str">
+      <c r="C129" s="8" t="str">
         <f>IF(A129="",
     IF(B129&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -5967,7 +5935,7 @@
     <row r="130" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A130" s="4"/>
       <c r="B130" s="5"/>
-      <c r="C130" s="10" t="str">
+      <c r="C130" s="8" t="str">
         <f>IF(A130="",
     IF(B130&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -5989,7 +5957,7 @@
     <row r="131" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A131" s="4"/>
       <c r="B131" s="5"/>
-      <c r="C131" s="10" t="str">
+      <c r="C131" s="8" t="str">
         <f>IF(A131="",
     IF(B131&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -6011,7 +5979,7 @@
     <row r="132" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A132" s="4"/>
       <c r="B132" s="5"/>
-      <c r="C132" s="10" t="str">
+      <c r="C132" s="8" t="str">
         <f>IF(A132="",
     IF(B132&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -6033,7 +6001,7 @@
     <row r="133" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A133" s="4"/>
       <c r="B133" s="5"/>
-      <c r="C133" s="10" t="str">
+      <c r="C133" s="8" t="str">
         <f>IF(A133="",
     IF(B133&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -6055,7 +6023,7 @@
     <row r="134" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A134" s="4"/>
       <c r="B134" s="5"/>
-      <c r="C134" s="10" t="str">
+      <c r="C134" s="8" t="str">
         <f>IF(A134="",
     IF(B134&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -6077,7 +6045,7 @@
     <row r="135" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A135" s="4"/>
       <c r="B135" s="5"/>
-      <c r="C135" s="10" t="str">
+      <c r="C135" s="8" t="str">
         <f>IF(A135="",
     IF(B135&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -6099,7 +6067,7 @@
     <row r="136" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A136" s="4"/>
       <c r="B136" s="5"/>
-      <c r="C136" s="10" t="str">
+      <c r="C136" s="8" t="str">
         <f>IF(A136="",
     IF(B136&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -6121,7 +6089,7 @@
     <row r="137" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A137" s="4"/>
       <c r="B137" s="5"/>
-      <c r="C137" s="10" t="str">
+      <c r="C137" s="8" t="str">
         <f>IF(A137="",
     IF(B137&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -6143,7 +6111,7 @@
     <row r="138" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A138" s="4"/>
       <c r="B138" s="5"/>
-      <c r="C138" s="10" t="str">
+      <c r="C138" s="8" t="str">
         <f>IF(A138="",
     IF(B138&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -6165,7 +6133,7 @@
     <row r="139" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A139" s="4"/>
       <c r="B139" s="5"/>
-      <c r="C139" s="10" t="str">
+      <c r="C139" s="8" t="str">
         <f>IF(A139="",
     IF(B139&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -6187,7 +6155,7 @@
     <row r="140" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A140" s="4"/>
       <c r="B140" s="5"/>
-      <c r="C140" s="10" t="str">
+      <c r="C140" s="8" t="str">
         <f>IF(A140="",
     IF(B140&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -6209,7 +6177,7 @@
     <row r="141" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A141" s="4"/>
       <c r="B141" s="5"/>
-      <c r="C141" s="10" t="str">
+      <c r="C141" s="8" t="str">
         <f>IF(A141="",
     IF(B141&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -6231,7 +6199,7 @@
     <row r="142" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A142" s="4"/>
       <c r="B142" s="5"/>
-      <c r="C142" s="10" t="str">
+      <c r="C142" s="8" t="str">
         <f>IF(A142="",
     IF(B142&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -6253,7 +6221,7 @@
     <row r="143" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A143" s="4"/>
       <c r="B143" s="5"/>
-      <c r="C143" s="10" t="str">
+      <c r="C143" s="8" t="str">
         <f>IF(A143="",
     IF(B143&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -6275,7 +6243,7 @@
     <row r="144" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A144" s="4"/>
       <c r="B144" s="5"/>
-      <c r="C144" s="10" t="str">
+      <c r="C144" s="8" t="str">
         <f>IF(A144="",
     IF(B144&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -6297,7 +6265,7 @@
     <row r="145" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A145" s="4"/>
       <c r="B145" s="5"/>
-      <c r="C145" s="10" t="str">
+      <c r="C145" s="8" t="str">
         <f>IF(A145="",
     IF(B145&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -6319,7 +6287,7 @@
     <row r="146" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A146" s="4"/>
       <c r="B146" s="5"/>
-      <c r="C146" s="10" t="str">
+      <c r="C146" s="8" t="str">
         <f>IF(A146="",
     IF(B146&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -6341,7 +6309,7 @@
     <row r="147" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A147" s="4"/>
       <c r="B147" s="5"/>
-      <c r="C147" s="10" t="str">
+      <c r="C147" s="8" t="str">
         <f>IF(A147="",
     IF(B147&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -6363,7 +6331,7 @@
     <row r="148" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A148" s="4"/>
       <c r="B148" s="5"/>
-      <c r="C148" s="10" t="str">
+      <c r="C148" s="8" t="str">
         <f>IF(A148="",
     IF(B148&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -6385,7 +6353,7 @@
     <row r="149" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A149" s="4"/>
       <c r="B149" s="5"/>
-      <c r="C149" s="10" t="str">
+      <c r="C149" s="8" t="str">
         <f>IF(A149="",
     IF(B149&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -6407,7 +6375,7 @@
     <row r="150" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A150" s="4"/>
       <c r="B150" s="5"/>
-      <c r="C150" s="10" t="str">
+      <c r="C150" s="8" t="str">
         <f>IF(A150="",
     IF(B150&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -6429,7 +6397,7 @@
     <row r="151" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A151" s="4"/>
       <c r="B151" s="5"/>
-      <c r="C151" s="10" t="str">
+      <c r="C151" s="8" t="str">
         <f>IF(A151="",
     IF(B151&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -6451,7 +6419,7 @@
     <row r="152" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A152" s="4"/>
       <c r="B152" s="5"/>
-      <c r="C152" s="10" t="str">
+      <c r="C152" s="8" t="str">
         <f>IF(A152="",
     IF(B152&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -6473,7 +6441,7 @@
     <row r="153" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A153" s="4"/>
       <c r="B153" s="5"/>
-      <c r="C153" s="10" t="str">
+      <c r="C153" s="8" t="str">
         <f>IF(A153="",
     IF(B153&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -6495,7 +6463,7 @@
     <row r="154" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A154" s="4"/>
       <c r="B154" s="5"/>
-      <c r="C154" s="10" t="str">
+      <c r="C154" s="8" t="str">
         <f>IF(A154="",
     IF(B154&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -6517,7 +6485,7 @@
     <row r="155" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A155" s="4"/>
       <c r="B155" s="5"/>
-      <c r="C155" s="10" t="str">
+      <c r="C155" s="8" t="str">
         <f>IF(A155="",
     IF(B155&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -6539,7 +6507,7 @@
     <row r="156" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A156" s="4"/>
       <c r="B156" s="5"/>
-      <c r="C156" s="10" t="str">
+      <c r="C156" s="8" t="str">
         <f>IF(A156="",
     IF(B156&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -6561,7 +6529,7 @@
     <row r="157" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A157" s="4"/>
       <c r="B157" s="5"/>
-      <c r="C157" s="10" t="str">
+      <c r="C157" s="8" t="str">
         <f>IF(A157="",
     IF(B157&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -6583,7 +6551,7 @@
     <row r="158" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A158" s="4"/>
       <c r="B158" s="5"/>
-      <c r="C158" s="10" t="str">
+      <c r="C158" s="8" t="str">
         <f>IF(A158="",
     IF(B158&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -6605,7 +6573,7 @@
     <row r="159" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A159" s="4"/>
       <c r="B159" s="5"/>
-      <c r="C159" s="10" t="str">
+      <c r="C159" s="8" t="str">
         <f>IF(A159="",
     IF(B159&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -6627,7 +6595,7 @@
     <row r="160" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A160" s="4"/>
       <c r="B160" s="5"/>
-      <c r="C160" s="10" t="str">
+      <c r="C160" s="8" t="str">
         <f>IF(A160="",
     IF(B160&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -6649,7 +6617,7 @@
     <row r="161" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A161" s="4"/>
       <c r="B161" s="5"/>
-      <c r="C161" s="10" t="str">
+      <c r="C161" s="8" t="str">
         <f>IF(A161="",
     IF(B161&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -6671,7 +6639,7 @@
     <row r="162" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A162" s="4"/>
       <c r="B162" s="5"/>
-      <c r="C162" s="10" t="str">
+      <c r="C162" s="8" t="str">
         <f>IF(A162="",
     IF(B162&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -6693,7 +6661,7 @@
     <row r="163" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A163" s="4"/>
       <c r="B163" s="5"/>
-      <c r="C163" s="10" t="str">
+      <c r="C163" s="8" t="str">
         <f>IF(A163="",
     IF(B163&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -6715,7 +6683,7 @@
     <row r="164" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A164" s="4"/>
       <c r="B164" s="5"/>
-      <c r="C164" s="10" t="str">
+      <c r="C164" s="8" t="str">
         <f>IF(A164="",
     IF(B164&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -6737,7 +6705,7 @@
     <row r="165" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A165" s="4"/>
       <c r="B165" s="5"/>
-      <c r="C165" s="10" t="str">
+      <c r="C165" s="8" t="str">
         <f>IF(A165="",
     IF(B165&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -6759,7 +6727,7 @@
     <row r="166" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A166" s="4"/>
       <c r="B166" s="5"/>
-      <c r="C166" s="10" t="str">
+      <c r="C166" s="8" t="str">
         <f>IF(A166="",
     IF(B166&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -6781,7 +6749,7 @@
     <row r="167" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A167" s="4"/>
       <c r="B167" s="5"/>
-      <c r="C167" s="10" t="str">
+      <c r="C167" s="8" t="str">
         <f>IF(A167="",
     IF(B167&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -6803,7 +6771,7 @@
     <row r="168" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A168" s="4"/>
       <c r="B168" s="5"/>
-      <c r="C168" s="10" t="str">
+      <c r="C168" s="8" t="str">
         <f>IF(A168="",
     IF(B168&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -6825,7 +6793,7 @@
     <row r="169" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A169" s="4"/>
       <c r="B169" s="5"/>
-      <c r="C169" s="10" t="str">
+      <c r="C169" s="8" t="str">
         <f>IF(A169="",
     IF(B169&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -6847,7 +6815,7 @@
     <row r="170" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A170" s="4"/>
       <c r="B170" s="5"/>
-      <c r="C170" s="10" t="str">
+      <c r="C170" s="8" t="str">
         <f>IF(A170="",
     IF(B170&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -6869,7 +6837,7 @@
     <row r="171" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A171" s="4"/>
       <c r="B171" s="5"/>
-      <c r="C171" s="10" t="str">
+      <c r="C171" s="8" t="str">
         <f>IF(A171="",
     IF(B171&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -6891,7 +6859,7 @@
     <row r="172" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A172" s="4"/>
       <c r="B172" s="5"/>
-      <c r="C172" s="10" t="str">
+      <c r="C172" s="8" t="str">
         <f>IF(A172="",
     IF(B172&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -6913,7 +6881,7 @@
     <row r="173" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A173" s="4"/>
       <c r="B173" s="5"/>
-      <c r="C173" s="10" t="str">
+      <c r="C173" s="8" t="str">
         <f>IF(A173="",
     IF(B173&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -6935,7 +6903,7 @@
     <row r="174" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A174" s="4"/>
       <c r="B174" s="5"/>
-      <c r="C174" s="10" t="str">
+      <c r="C174" s="8" t="str">
         <f>IF(A174="",
     IF(B174&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -6957,7 +6925,7 @@
     <row r="175" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A175" s="4"/>
       <c r="B175" s="5"/>
-      <c r="C175" s="10" t="str">
+      <c r="C175" s="8" t="str">
         <f>IF(A175="",
     IF(B175&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -6979,7 +6947,7 @@
     <row r="176" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A176" s="4"/>
       <c r="B176" s="5"/>
-      <c r="C176" s="10" t="str">
+      <c r="C176" s="8" t="str">
         <f>IF(A176="",
     IF(B176&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -7001,7 +6969,7 @@
     <row r="177" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A177" s="4"/>
       <c r="B177" s="5"/>
-      <c r="C177" s="10" t="str">
+      <c r="C177" s="8" t="str">
         <f>IF(A177="",
     IF(B177&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -7023,7 +6991,7 @@
     <row r="178" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A178" s="4"/>
       <c r="B178" s="5"/>
-      <c r="C178" s="10" t="str">
+      <c r="C178" s="8" t="str">
         <f>IF(A178="",
     IF(B178&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -7045,7 +7013,7 @@
     <row r="179" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A179" s="4"/>
       <c r="B179" s="5"/>
-      <c r="C179" s="10" t="str">
+      <c r="C179" s="8" t="str">
         <f>IF(A179="",
     IF(B179&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -7067,7 +7035,7 @@
     <row r="180" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A180" s="4"/>
       <c r="B180" s="5"/>
-      <c r="C180" s="10" t="str">
+      <c r="C180" s="8" t="str">
         <f>IF(A180="",
     IF(B180&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -7089,7 +7057,7 @@
     <row r="181" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A181" s="4"/>
       <c r="B181" s="5"/>
-      <c r="C181" s="10" t="str">
+      <c r="C181" s="8" t="str">
         <f>IF(A181="",
     IF(B181&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -7111,7 +7079,7 @@
     <row r="182" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A182" s="4"/>
       <c r="B182" s="5"/>
-      <c r="C182" s="10" t="str">
+      <c r="C182" s="8" t="str">
         <f>IF(A182="",
     IF(B182&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -7133,7 +7101,7 @@
     <row r="183" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A183" s="4"/>
       <c r="B183" s="5"/>
-      <c r="C183" s="10" t="str">
+      <c r="C183" s="8" t="str">
         <f>IF(A183="",
     IF(B183&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -7155,7 +7123,7 @@
     <row r="184" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A184" s="4"/>
       <c r="B184" s="5"/>
-      <c r="C184" s="10" t="str">
+      <c r="C184" s="8" t="str">
         <f>IF(A184="",
     IF(B184&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -7177,7 +7145,7 @@
     <row r="185" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A185" s="4"/>
       <c r="B185" s="5"/>
-      <c r="C185" s="10" t="str">
+      <c r="C185" s="8" t="str">
         <f>IF(A185="",
     IF(B185&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -7199,7 +7167,7 @@
     <row r="186" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A186" s="4"/>
       <c r="B186" s="5"/>
-      <c r="C186" s="10" t="str">
+      <c r="C186" s="8" t="str">
         <f>IF(A186="",
     IF(B186&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -7221,7 +7189,7 @@
     <row r="187" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A187" s="4"/>
       <c r="B187" s="5"/>
-      <c r="C187" s="10" t="str">
+      <c r="C187" s="8" t="str">
         <f>IF(A187="",
     IF(B187&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -7243,7 +7211,7 @@
     <row r="188" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A188" s="4"/>
       <c r="B188" s="5"/>
-      <c r="C188" s="10" t="str">
+      <c r="C188" s="8" t="str">
         <f>IF(A188="",
     IF(B188&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -7265,7 +7233,7 @@
     <row r="189" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A189" s="4"/>
       <c r="B189" s="5"/>
-      <c r="C189" s="10" t="str">
+      <c r="C189" s="8" t="str">
         <f>IF(A189="",
     IF(B189&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -7287,7 +7255,7 @@
     <row r="190" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A190" s="4"/>
       <c r="B190" s="5"/>
-      <c r="C190" s="10" t="str">
+      <c r="C190" s="8" t="str">
         <f>IF(A190="",
     IF(B190&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -7309,7 +7277,7 @@
     <row r="191" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A191" s="4"/>
       <c r="B191" s="5"/>
-      <c r="C191" s="10" t="str">
+      <c r="C191" s="8" t="str">
         <f>IF(A191="",
     IF(B191&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -7331,7 +7299,7 @@
     <row r="192" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A192" s="4"/>
       <c r="B192" s="5"/>
-      <c r="C192" s="10" t="str">
+      <c r="C192" s="8" t="str">
         <f>IF(A192="",
     IF(B192&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -7353,7 +7321,7 @@
     <row r="193" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A193" s="4"/>
       <c r="B193" s="5"/>
-      <c r="C193" s="10" t="str">
+      <c r="C193" s="8" t="str">
         <f>IF(A193="",
     IF(B193&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -7375,7 +7343,7 @@
     <row r="194" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A194" s="4"/>
       <c r="B194" s="5"/>
-      <c r="C194" s="10" t="str">
+      <c r="C194" s="8" t="str">
         <f>IF(A194="",
     IF(B194&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -7397,7 +7365,7 @@
     <row r="195" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A195" s="4"/>
       <c r="B195" s="5"/>
-      <c r="C195" s="10" t="str">
+      <c r="C195" s="8" t="str">
         <f>IF(A195="",
     IF(B195&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -7419,7 +7387,7 @@
     <row r="196" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A196" s="4"/>
       <c r="B196" s="5"/>
-      <c r="C196" s="10" t="str">
+      <c r="C196" s="8" t="str">
         <f>IF(A196="",
     IF(B196&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -7441,7 +7409,7 @@
     <row r="197" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A197" s="4"/>
       <c r="B197" s="5"/>
-      <c r="C197" s="10" t="str">
+      <c r="C197" s="8" t="str">
         <f>IF(A197="",
     IF(B197&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -7463,7 +7431,7 @@
     <row r="198" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A198" s="4"/>
       <c r="B198" s="5"/>
-      <c r="C198" s="10" t="str">
+      <c r="C198" s="8" t="str">
         <f>IF(A198="",
     IF(B198&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -7485,7 +7453,7 @@
     <row r="199" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A199" s="4"/>
       <c r="B199" s="5"/>
-      <c r="C199" s="10" t="str">
+      <c r="C199" s="8" t="str">
         <f>IF(A199="",
     IF(B199&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -7507,7 +7475,7 @@
     <row r="200" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A200" s="4"/>
       <c r="B200" s="5"/>
-      <c r="C200" s="10" t="str">
+      <c r="C200" s="8" t="str">
         <f>IF(A200="",
     IF(B200&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -7529,7 +7497,7 @@
     <row r="201" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A201" s="4"/>
       <c r="B201" s="5"/>
-      <c r="C201" s="10" t="str">
+      <c r="C201" s="8" t="str">
         <f>IF(A201="",
     IF(B201&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -7551,7 +7519,7 @@
     <row r="202" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A202" s="4"/>
       <c r="B202" s="5"/>
-      <c r="C202" s="10" t="str">
+      <c r="C202" s="8" t="str">
         <f>IF(A202="",
     IF(B202&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -7573,7 +7541,7 @@
     <row r="203" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A203" s="4"/>
       <c r="B203" s="5"/>
-      <c r="C203" s="10" t="str">
+      <c r="C203" s="8" t="str">
         <f>IF(A203="",
     IF(B203&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -7595,7 +7563,7 @@
     <row r="204" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A204" s="4"/>
       <c r="B204" s="5"/>
-      <c r="C204" s="10" t="str">
+      <c r="C204" s="8" t="str">
         <f>IF(A204="",
     IF(B204&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -7617,7 +7585,7 @@
     <row r="205" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A205" s="4"/>
       <c r="B205" s="5"/>
-      <c r="C205" s="10" t="str">
+      <c r="C205" s="8" t="str">
         <f>IF(A205="",
     IF(B205&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -7639,7 +7607,7 @@
     <row r="206" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A206" s="4"/>
       <c r="B206" s="5"/>
-      <c r="C206" s="10" t="str">
+      <c r="C206" s="8" t="str">
         <f>IF(A206="",
     IF(B206&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -7661,7 +7629,7 @@
     <row r="207" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A207" s="4"/>
       <c r="B207" s="5"/>
-      <c r="C207" s="10" t="str">
+      <c r="C207" s="8" t="str">
         <f>IF(A207="",
     IF(B207&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -7683,7 +7651,7 @@
     <row r="208" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A208" s="4"/>
       <c r="B208" s="5"/>
-      <c r="C208" s="10" t="str">
+      <c r="C208" s="8" t="str">
         <f>IF(A208="",
     IF(B208&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -7705,7 +7673,7 @@
     <row r="209" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A209" s="4"/>
       <c r="B209" s="5"/>
-      <c r="C209" s="10" t="str">
+      <c r="C209" s="8" t="str">
         <f>IF(A209="",
     IF(B209&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -7727,7 +7695,7 @@
     <row r="210" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A210" s="4"/>
       <c r="B210" s="5"/>
-      <c r="C210" s="10" t="str">
+      <c r="C210" s="8" t="str">
         <f>IF(A210="",
     IF(B210&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -7749,7 +7717,7 @@
     <row r="211" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A211" s="4"/>
       <c r="B211" s="5"/>
-      <c r="C211" s="10" t="str">
+      <c r="C211" s="8" t="str">
         <f>IF(A211="",
     IF(B211&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -7771,7 +7739,7 @@
     <row r="212" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A212" s="4"/>
       <c r="B212" s="5"/>
-      <c r="C212" s="10" t="str">
+      <c r="C212" s="8" t="str">
         <f>IF(A212="",
     IF(B212&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -7793,7 +7761,7 @@
     <row r="213" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A213" s="4"/>
       <c r="B213" s="5"/>
-      <c r="C213" s="10" t="str">
+      <c r="C213" s="8" t="str">
         <f>IF(A213="",
     IF(B213&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -7815,7 +7783,7 @@
     <row r="214" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A214" s="4"/>
       <c r="B214" s="5"/>
-      <c r="C214" s="10" t="str">
+      <c r="C214" s="8" t="str">
         <f>IF(A214="",
     IF(B214&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -7837,7 +7805,7 @@
     <row r="215" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A215" s="4"/>
       <c r="B215" s="5"/>
-      <c r="C215" s="10" t="str">
+      <c r="C215" s="8" t="str">
         <f>IF(A215="",
     IF(B215&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -7859,7 +7827,7 @@
     <row r="216" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A216" s="4"/>
       <c r="B216" s="5"/>
-      <c r="C216" s="10" t="str">
+      <c r="C216" s="8" t="str">
         <f>IF(A216="",
     IF(B216&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -7881,7 +7849,7 @@
     <row r="217" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A217" s="4"/>
       <c r="B217" s="5"/>
-      <c r="C217" s="10" t="str">
+      <c r="C217" s="8" t="str">
         <f>IF(A217="",
     IF(B217&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -7903,7 +7871,7 @@
     <row r="218" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A218" s="4"/>
       <c r="B218" s="5"/>
-      <c r="C218" s="10" t="str">
+      <c r="C218" s="8" t="str">
         <f>IF(A218="",
     IF(B218&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -7925,7 +7893,7 @@
     <row r="219" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A219" s="4"/>
       <c r="B219" s="5"/>
-      <c r="C219" s="10" t="str">
+      <c r="C219" s="8" t="str">
         <f>IF(A219="",
     IF(B219&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -7947,7 +7915,7 @@
     <row r="220" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A220" s="4"/>
       <c r="B220" s="5"/>
-      <c r="C220" s="10" t="str">
+      <c r="C220" s="8" t="str">
         <f>IF(A220="",
     IF(B220&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -7969,7 +7937,7 @@
     <row r="221" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A221" s="4"/>
       <c r="B221" s="5"/>
-      <c r="C221" s="10" t="str">
+      <c r="C221" s="8" t="str">
         <f>IF(A221="",
     IF(B221&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -7991,7 +7959,7 @@
     <row r="222" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A222" s="4"/>
       <c r="B222" s="5"/>
-      <c r="C222" s="10" t="str">
+      <c r="C222" s="8" t="str">
         <f>IF(A222="",
     IF(B222&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -8013,7 +7981,7 @@
     <row r="223" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A223" s="4"/>
       <c r="B223" s="5"/>
-      <c r="C223" s="10" t="str">
+      <c r="C223" s="8" t="str">
         <f>IF(A223="",
     IF(B223&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -8035,7 +8003,7 @@
     <row r="224" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A224" s="4"/>
       <c r="B224" s="5"/>
-      <c r="C224" s="10" t="str">
+      <c r="C224" s="8" t="str">
         <f>IF(A224="",
     IF(B224&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -8057,7 +8025,7 @@
     <row r="225" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A225" s="4"/>
       <c r="B225" s="5"/>
-      <c r="C225" s="10" t="str">
+      <c r="C225" s="8" t="str">
         <f>IF(A225="",
     IF(B225&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -8079,7 +8047,7 @@
     <row r="226" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A226" s="4"/>
       <c r="B226" s="5"/>
-      <c r="C226" s="10" t="str">
+      <c r="C226" s="8" t="str">
         <f>IF(A226="",
     IF(B226&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -8101,7 +8069,7 @@
     <row r="227" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A227" s="4"/>
       <c r="B227" s="5"/>
-      <c r="C227" s="10" t="str">
+      <c r="C227" s="8" t="str">
         <f>IF(A227="",
     IF(B227&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -8123,7 +8091,7 @@
     <row r="228" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A228" s="4"/>
       <c r="B228" s="5"/>
-      <c r="C228" s="10" t="str">
+      <c r="C228" s="8" t="str">
         <f>IF(A228="",
     IF(B228&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -8145,7 +8113,7 @@
     <row r="229" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A229" s="4"/>
       <c r="B229" s="5"/>
-      <c r="C229" s="10" t="str">
+      <c r="C229" s="8" t="str">
         <f>IF(A229="",
     IF(B229&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -8167,7 +8135,7 @@
     <row r="230" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A230" s="4"/>
       <c r="B230" s="5"/>
-      <c r="C230" s="10" t="str">
+      <c r="C230" s="8" t="str">
         <f>IF(A230="",
     IF(B230&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -8189,7 +8157,7 @@
     <row r="231" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A231" s="4"/>
       <c r="B231" s="5"/>
-      <c r="C231" s="10" t="str">
+      <c r="C231" s="8" t="str">
         <f>IF(A231="",
     IF(B231&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -8211,7 +8179,7 @@
     <row r="232" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A232" s="4"/>
       <c r="B232" s="5"/>
-      <c r="C232" s="10" t="str">
+      <c r="C232" s="8" t="str">
         <f>IF(A232="",
     IF(B232&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -8233,7 +8201,7 @@
     <row r="233" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A233" s="4"/>
       <c r="B233" s="5"/>
-      <c r="C233" s="10" t="str">
+      <c r="C233" s="8" t="str">
         <f>IF(A233="",
     IF(B233&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -8255,7 +8223,7 @@
     <row r="234" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A234" s="4"/>
       <c r="B234" s="5"/>
-      <c r="C234" s="10" t="str">
+      <c r="C234" s="8" t="str">
         <f>IF(A234="",
     IF(B234&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -8277,7 +8245,7 @@
     <row r="235" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A235" s="4"/>
       <c r="B235" s="5"/>
-      <c r="C235" s="10" t="str">
+      <c r="C235" s="8" t="str">
         <f>IF(A235="",
     IF(B235&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -8299,7 +8267,7 @@
     <row r="236" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A236" s="4"/>
       <c r="B236" s="5"/>
-      <c r="C236" s="10" t="str">
+      <c r="C236" s="8" t="str">
         <f>IF(A236="",
     IF(B236&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -8321,7 +8289,7 @@
     <row r="237" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A237" s="4"/>
       <c r="B237" s="5"/>
-      <c r="C237" s="10" t="str">
+      <c r="C237" s="8" t="str">
         <f>IF(A237="",
     IF(B237&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -8343,7 +8311,7 @@
     <row r="238" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A238" s="4"/>
       <c r="B238" s="5"/>
-      <c r="C238" s="10" t="str">
+      <c r="C238" s="8" t="str">
         <f>IF(A238="",
     IF(B238&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -8365,7 +8333,7 @@
     <row r="239" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A239" s="4"/>
       <c r="B239" s="5"/>
-      <c r="C239" s="10" t="str">
+      <c r="C239" s="8" t="str">
         <f>IF(A239="",
     IF(B239&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -8387,7 +8355,7 @@
     <row r="240" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A240" s="4"/>
       <c r="B240" s="5"/>
-      <c r="C240" s="10" t="str">
+      <c r="C240" s="8" t="str">
         <f>IF(A240="",
     IF(B240&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -8409,7 +8377,7 @@
     <row r="241" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A241" s="4"/>
       <c r="B241" s="5"/>
-      <c r="C241" s="10" t="str">
+      <c r="C241" s="8" t="str">
         <f>IF(A241="",
     IF(B241&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -8431,7 +8399,7 @@
     <row r="242" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A242" s="4"/>
       <c r="B242" s="5"/>
-      <c r="C242" s="10" t="str">
+      <c r="C242" s="8" t="str">
         <f>IF(A242="",
     IF(B242&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -8453,7 +8421,7 @@
     <row r="243" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A243" s="4"/>
       <c r="B243" s="5"/>
-      <c r="C243" s="10" t="str">
+      <c r="C243" s="8" t="str">
         <f>IF(A243="",
     IF(B243&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -8475,7 +8443,7 @@
     <row r="244" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A244" s="4"/>
       <c r="B244" s="5"/>
-      <c r="C244" s="10" t="str">
+      <c r="C244" s="8" t="str">
         <f>IF(A244="",
     IF(B244&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -8497,7 +8465,7 @@
     <row r="245" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A245" s="4"/>
       <c r="B245" s="5"/>
-      <c r="C245" s="10" t="str">
+      <c r="C245" s="8" t="str">
         <f>IF(A245="",
     IF(B245&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -8519,7 +8487,7 @@
     <row r="246" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A246" s="4"/>
       <c r="B246" s="5"/>
-      <c r="C246" s="10" t="str">
+      <c r="C246" s="8" t="str">
         <f>IF(A246="",
     IF(B246&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -8541,7 +8509,7 @@
     <row r="247" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A247" s="4"/>
       <c r="B247" s="5"/>
-      <c r="C247" s="10" t="str">
+      <c r="C247" s="8" t="str">
         <f>IF(A247="",
     IF(B247&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -8563,7 +8531,7 @@
     <row r="248" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A248" s="4"/>
       <c r="B248" s="5"/>
-      <c r="C248" s="10" t="str">
+      <c r="C248" s="8" t="str">
         <f>IF(A248="",
     IF(B248&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -8585,7 +8553,7 @@
     <row r="249" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A249" s="4"/>
       <c r="B249" s="5"/>
-      <c r="C249" s="10" t="str">
+      <c r="C249" s="8" t="str">
         <f>IF(A249="",
     IF(B249&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -8607,7 +8575,7 @@
     <row r="250" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A250" s="4"/>
       <c r="B250" s="5"/>
-      <c r="C250" s="10" t="str">
+      <c r="C250" s="8" t="str">
         <f>IF(A250="",
     IF(B250&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -8629,7 +8597,7 @@
     <row r="251" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A251" s="4"/>
       <c r="B251" s="5"/>
-      <c r="C251" s="10" t="str">
+      <c r="C251" s="8" t="str">
         <f>IF(A251="",
     IF(B251&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -8651,7 +8619,7 @@
     <row r="252" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A252" s="4"/>
       <c r="B252" s="5"/>
-      <c r="C252" s="10" t="str">
+      <c r="C252" s="8" t="str">
         <f>IF(A252="",
     IF(B252&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -8673,7 +8641,7 @@
     <row r="253" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A253" s="4"/>
       <c r="B253" s="5"/>
-      <c r="C253" s="10" t="str">
+      <c r="C253" s="8" t="str">
         <f>IF(A253="",
     IF(B253&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -8695,7 +8663,7 @@
     <row r="254" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A254" s="4"/>
       <c r="B254" s="5"/>
-      <c r="C254" s="10" t="str">
+      <c r="C254" s="8" t="str">
         <f>IF(A254="",
     IF(B254&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -8717,7 +8685,7 @@
     <row r="255" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A255" s="4"/>
       <c r="B255" s="5"/>
-      <c r="C255" s="10" t="str">
+      <c r="C255" s="8" t="str">
         <f>IF(A255="",
     IF(B255&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -8739,7 +8707,7 @@
     <row r="256" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A256" s="4"/>
       <c r="B256" s="5"/>
-      <c r="C256" s="10" t="str">
+      <c r="C256" s="8" t="str">
         <f>IF(A256="",
     IF(B256&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -8761,7 +8729,7 @@
     <row r="257" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A257" s="4"/>
       <c r="B257" s="5"/>
-      <c r="C257" s="10" t="str">
+      <c r="C257" s="8" t="str">
         <f>IF(A257="",
     IF(B257&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -8783,7 +8751,7 @@
     <row r="258" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A258" s="4"/>
       <c r="B258" s="5"/>
-      <c r="C258" s="10" t="str">
+      <c r="C258" s="8" t="str">
         <f>IF(A258="",
     IF(B258&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -8805,7 +8773,7 @@
     <row r="259" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A259" s="4"/>
       <c r="B259" s="5"/>
-      <c r="C259" s="10" t="str">
+      <c r="C259" s="8" t="str">
         <f>IF(A259="",
     IF(B259&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -8827,7 +8795,7 @@
     <row r="260" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A260" s="4"/>
       <c r="B260" s="5"/>
-      <c r="C260" s="10" t="str">
+      <c r="C260" s="8" t="str">
         <f>IF(A260="",
     IF(B260&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -8849,7 +8817,7 @@
     <row r="261" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A261" s="4"/>
       <c r="B261" s="5"/>
-      <c r="C261" s="10" t="str">
+      <c r="C261" s="8" t="str">
         <f>IF(A261="",
     IF(B261&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -8871,7 +8839,7 @@
     <row r="262" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A262" s="4"/>
       <c r="B262" s="5"/>
-      <c r="C262" s="10" t="str">
+      <c r="C262" s="8" t="str">
         <f>IF(A262="",
     IF(B262&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -8893,7 +8861,7 @@
     <row r="263" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A263" s="4"/>
       <c r="B263" s="5"/>
-      <c r="C263" s="10" t="str">
+      <c r="C263" s="8" t="str">
         <f>IF(A263="",
     IF(B263&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -8915,7 +8883,7 @@
     <row r="264" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A264" s="4"/>
       <c r="B264" s="5"/>
-      <c r="C264" s="10" t="str">
+      <c r="C264" s="8" t="str">
         <f>IF(A264="",
     IF(B264&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -8937,7 +8905,7 @@
     <row r="265" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A265" s="4"/>
       <c r="B265" s="5"/>
-      <c r="C265" s="10" t="str">
+      <c r="C265" s="8" t="str">
         <f>IF(A265="",
     IF(B265&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -8959,7 +8927,7 @@
     <row r="266" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A266" s="4"/>
       <c r="B266" s="5"/>
-      <c r="C266" s="10" t="str">
+      <c r="C266" s="8" t="str">
         <f>IF(A266="",
     IF(B266&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -8981,7 +8949,7 @@
     <row r="267" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A267" s="4"/>
       <c r="B267" s="5"/>
-      <c r="C267" s="10" t="str">
+      <c r="C267" s="8" t="str">
         <f>IF(A267="",
     IF(B267&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -9003,7 +8971,7 @@
     <row r="268" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A268" s="4"/>
       <c r="B268" s="5"/>
-      <c r="C268" s="10" t="str">
+      <c r="C268" s="8" t="str">
         <f>IF(A268="",
     IF(B268&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -9025,7 +8993,7 @@
     <row r="269" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A269" s="4"/>
       <c r="B269" s="5"/>
-      <c r="C269" s="10" t="str">
+      <c r="C269" s="8" t="str">
         <f>IF(A269="",
     IF(B269&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -9047,7 +9015,7 @@
     <row r="270" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A270" s="4"/>
       <c r="B270" s="5"/>
-      <c r="C270" s="10" t="str">
+      <c r="C270" s="8" t="str">
         <f>IF(A270="",
     IF(B270&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -9069,7 +9037,7 @@
     <row r="271" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A271" s="4"/>
       <c r="B271" s="5"/>
-      <c r="C271" s="10" t="str">
+      <c r="C271" s="8" t="str">
         <f>IF(A271="",
     IF(B271&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -9091,7 +9059,7 @@
     <row r="272" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A272" s="4"/>
       <c r="B272" s="5"/>
-      <c r="C272" s="10" t="str">
+      <c r="C272" s="8" t="str">
         <f>IF(A272="",
     IF(B272&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -9113,7 +9081,7 @@
     <row r="273" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A273" s="4"/>
       <c r="B273" s="5"/>
-      <c r="C273" s="10" t="str">
+      <c r="C273" s="8" t="str">
         <f>IF(A273="",
     IF(B273&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -9135,7 +9103,7 @@
     <row r="274" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A274" s="4"/>
       <c r="B274" s="5"/>
-      <c r="C274" s="10" t="str">
+      <c r="C274" s="8" t="str">
         <f>IF(A274="",
     IF(B274&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -9157,7 +9125,7 @@
     <row r="275" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A275" s="4"/>
       <c r="B275" s="5"/>
-      <c r="C275" s="10" t="str">
+      <c r="C275" s="8" t="str">
         <f>IF(A275="",
     IF(B275&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -9179,7 +9147,7 @@
     <row r="276" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A276" s="4"/>
       <c r="B276" s="5"/>
-      <c r="C276" s="10" t="str">
+      <c r="C276" s="8" t="str">
         <f>IF(A276="",
     IF(B276&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -9201,7 +9169,7 @@
     <row r="277" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A277" s="4"/>
       <c r="B277" s="5"/>
-      <c r="C277" s="10" t="str">
+      <c r="C277" s="8" t="str">
         <f>IF(A277="",
     IF(B277&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -9223,7 +9191,7 @@
     <row r="278" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A278" s="4"/>
       <c r="B278" s="5"/>
-      <c r="C278" s="10" t="str">
+      <c r="C278" s="8" t="str">
         <f>IF(A278="",
     IF(B278&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -9245,7 +9213,7 @@
     <row r="279" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A279" s="4"/>
       <c r="B279" s="5"/>
-      <c r="C279" s="10" t="str">
+      <c r="C279" s="8" t="str">
         <f>IF(A279="",
     IF(B279&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -9267,7 +9235,7 @@
     <row r="280" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A280" s="4"/>
       <c r="B280" s="5"/>
-      <c r="C280" s="10" t="str">
+      <c r="C280" s="8" t="str">
         <f>IF(A280="",
     IF(B280&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -9289,7 +9257,7 @@
     <row r="281" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A281" s="4"/>
       <c r="B281" s="5"/>
-      <c r="C281" s="10" t="str">
+      <c r="C281" s="8" t="str">
         <f>IF(A281="",
     IF(B281&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -9311,7 +9279,7 @@
     <row r="282" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A282" s="4"/>
       <c r="B282" s="5"/>
-      <c r="C282" s="10" t="str">
+      <c r="C282" s="8" t="str">
         <f>IF(A282="",
     IF(B282&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -9333,7 +9301,7 @@
     <row r="283" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A283" s="4"/>
       <c r="B283" s="5"/>
-      <c r="C283" s="10" t="str">
+      <c r="C283" s="8" t="str">
         <f>IF(A283="",
     IF(B283&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -9355,7 +9323,7 @@
     <row r="284" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A284" s="4"/>
       <c r="B284" s="5"/>
-      <c r="C284" s="10" t="str">
+      <c r="C284" s="8" t="str">
         <f>IF(A284="",
     IF(B284&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -9377,7 +9345,7 @@
     <row r="285" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A285" s="4"/>
       <c r="B285" s="5"/>
-      <c r="C285" s="10" t="str">
+      <c r="C285" s="8" t="str">
         <f>IF(A285="",
     IF(B285&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -9399,7 +9367,7 @@
     <row r="286" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A286" s="4"/>
       <c r="B286" s="5"/>
-      <c r="C286" s="10" t="str">
+      <c r="C286" s="8" t="str">
         <f>IF(A286="",
     IF(B286&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -9421,7 +9389,7 @@
     <row r="287" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A287" s="4"/>
       <c r="B287" s="5"/>
-      <c r="C287" s="10" t="str">
+      <c r="C287" s="8" t="str">
         <f>IF(A287="",
     IF(B287&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -9443,7 +9411,7 @@
     <row r="288" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A288" s="4"/>
       <c r="B288" s="5"/>
-      <c r="C288" s="10" t="str">
+      <c r="C288" s="8" t="str">
         <f>IF(A288="",
     IF(B288&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -9465,7 +9433,7 @@
     <row r="289" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A289" s="4"/>
       <c r="B289" s="5"/>
-      <c r="C289" s="10" t="str">
+      <c r="C289" s="8" t="str">
         <f>IF(A289="",
     IF(B289&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -9487,7 +9455,7 @@
     <row r="290" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A290" s="4"/>
       <c r="B290" s="5"/>
-      <c r="C290" s="10" t="str">
+      <c r="C290" s="8" t="str">
         <f>IF(A290="",
     IF(B290&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -9509,7 +9477,7 @@
     <row r="291" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A291" s="4"/>
       <c r="B291" s="5"/>
-      <c r="C291" s="10" t="str">
+      <c r="C291" s="8" t="str">
         <f>IF(A291="",
     IF(B291&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -9531,7 +9499,7 @@
     <row r="292" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A292" s="4"/>
       <c r="B292" s="5"/>
-      <c r="C292" s="10" t="str">
+      <c r="C292" s="8" t="str">
         <f>IF(A292="",
     IF(B292&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -9553,7 +9521,7 @@
     <row r="293" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A293" s="4"/>
       <c r="B293" s="5"/>
-      <c r="C293" s="10" t="str">
+      <c r="C293" s="8" t="str">
         <f>IF(A293="",
     IF(B293&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -9575,7 +9543,7 @@
     <row r="294" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A294" s="4"/>
       <c r="B294" s="5"/>
-      <c r="C294" s="10" t="str">
+      <c r="C294" s="8" t="str">
         <f>IF(A294="",
     IF(B294&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -9597,7 +9565,7 @@
     <row r="295" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A295" s="4"/>
       <c r="B295" s="5"/>
-      <c r="C295" s="10" t="str">
+      <c r="C295" s="8" t="str">
         <f>IF(A295="",
     IF(B295&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -9619,7 +9587,7 @@
     <row r="296" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A296" s="4"/>
       <c r="B296" s="5"/>
-      <c r="C296" s="10" t="str">
+      <c r="C296" s="8" t="str">
         <f>IF(A296="",
     IF(B296&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -9641,7 +9609,7 @@
     <row r="297" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A297" s="4"/>
       <c r="B297" s="5"/>
-      <c r="C297" s="10" t="str">
+      <c r="C297" s="8" t="str">
         <f>IF(A297="",
     IF(B297&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -9663,7 +9631,7 @@
     <row r="298" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A298" s="4"/>
       <c r="B298" s="5"/>
-      <c r="C298" s="10" t="str">
+      <c r="C298" s="8" t="str">
         <f>IF(A298="",
     IF(B298&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -9685,7 +9653,7 @@
     <row r="299" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A299" s="4"/>
       <c r="B299" s="5"/>
-      <c r="C299" s="10" t="str">
+      <c r="C299" s="8" t="str">
         <f>IF(A299="",
     IF(B299&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -9707,7 +9675,7 @@
     <row r="300" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A300" s="4"/>
       <c r="B300" s="5"/>
-      <c r="C300" s="10" t="str">
+      <c r="C300" s="8" t="str">
         <f>IF(A300="",
     IF(B300&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -9729,7 +9697,7 @@
     <row r="301" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A301" s="4"/>
       <c r="B301" s="5"/>
-      <c r="C301" s="10" t="str">
+      <c r="C301" s="8" t="str">
         <f>IF(A301="",
     IF(B301&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -9751,7 +9719,7 @@
     <row r="302" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A302" s="4"/>
       <c r="B302" s="5"/>
-      <c r="C302" s="10" t="str">
+      <c r="C302" s="8" t="str">
         <f>IF(A302="",
     IF(B302&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -9773,7 +9741,7 @@
     <row r="303" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A303" s="4"/>
       <c r="B303" s="5"/>
-      <c r="C303" s="10" t="str">
+      <c r="C303" s="8" t="str">
         <f>IF(A303="",
     IF(B303&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -9795,7 +9763,7 @@
     <row r="304" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A304" s="4"/>
       <c r="B304" s="5"/>
-      <c r="C304" s="10" t="str">
+      <c r="C304" s="8" t="str">
         <f>IF(A304="",
     IF(B304&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -9817,7 +9785,7 @@
     <row r="305" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A305" s="4"/>
       <c r="B305" s="5"/>
-      <c r="C305" s="10" t="str">
+      <c r="C305" s="8" t="str">
         <f>IF(A305="",
     IF(B305&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -9839,7 +9807,7 @@
     <row r="306" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A306" s="4"/>
       <c r="B306" s="5"/>
-      <c r="C306" s="10" t="str">
+      <c r="C306" s="8" t="str">
         <f>IF(A306="",
     IF(B306&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -9861,7 +9829,7 @@
     <row r="307" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A307" s="4"/>
       <c r="B307" s="5"/>
-      <c r="C307" s="10" t="str">
+      <c r="C307" s="8" t="str">
         <f>IF(A307="",
     IF(B307&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -9883,7 +9851,7 @@
     <row r="308" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A308" s="4"/>
       <c r="B308" s="5"/>
-      <c r="C308" s="10" t="str">
+      <c r="C308" s="8" t="str">
         <f>IF(A308="",
     IF(B308&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -9905,7 +9873,7 @@
     <row r="309" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A309" s="4"/>
       <c r="B309" s="5"/>
-      <c r="C309" s="10" t="str">
+      <c r="C309" s="8" t="str">
         <f>IF(A309="",
     IF(B309&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -9927,7 +9895,7 @@
     <row r="310" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A310" s="4"/>
       <c r="B310" s="5"/>
-      <c r="C310" s="10" t="str">
+      <c r="C310" s="8" t="str">
         <f>IF(A310="",
     IF(B310&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -9949,7 +9917,7 @@
     <row r="311" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A311" s="4"/>
       <c r="B311" s="5"/>
-      <c r="C311" s="10" t="str">
+      <c r="C311" s="8" t="str">
         <f>IF(A311="",
     IF(B311&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -9971,7 +9939,7 @@
     <row r="312" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A312" s="4"/>
       <c r="B312" s="5"/>
-      <c r="C312" s="10" t="str">
+      <c r="C312" s="8" t="str">
         <f>IF(A312="",
     IF(B312&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -9993,7 +9961,7 @@
     <row r="313" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A313" s="4"/>
       <c r="B313" s="5"/>
-      <c r="C313" s="10" t="str">
+      <c r="C313" s="8" t="str">
         <f>IF(A313="",
     IF(B313&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -10015,7 +9983,7 @@
     <row r="314" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A314" s="4"/>
       <c r="B314" s="5"/>
-      <c r="C314" s="10" t="str">
+      <c r="C314" s="8" t="str">
         <f>IF(A314="",
     IF(B314&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -10037,7 +10005,7 @@
     <row r="315" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A315" s="4"/>
       <c r="B315" s="5"/>
-      <c r="C315" s="10" t="str">
+      <c r="C315" s="8" t="str">
         <f>IF(A315="",
     IF(B315&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -10059,7 +10027,7 @@
     <row r="316" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A316" s="4"/>
       <c r="B316" s="5"/>
-      <c r="C316" s="10" t="str">
+      <c r="C316" s="8" t="str">
         <f>IF(A316="",
     IF(B316&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -10081,7 +10049,7 @@
     <row r="317" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A317" s="4"/>
       <c r="B317" s="5"/>
-      <c r="C317" s="10" t="str">
+      <c r="C317" s="8" t="str">
         <f>IF(A317="",
     IF(B317&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -10103,7 +10071,7 @@
     <row r="318" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A318" s="4"/>
       <c r="B318" s="5"/>
-      <c r="C318" s="10" t="str">
+      <c r="C318" s="8" t="str">
         <f>IF(A318="",
     IF(B318&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -10125,7 +10093,7 @@
     <row r="319" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A319" s="4"/>
       <c r="B319" s="5"/>
-      <c r="C319" s="10" t="str">
+      <c r="C319" s="8" t="str">
         <f>IF(A319="",
     IF(B319&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -10147,7 +10115,7 @@
     <row r="320" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A320" s="4"/>
       <c r="B320" s="5"/>
-      <c r="C320" s="10" t="str">
+      <c r="C320" s="8" t="str">
         <f>IF(A320="",
     IF(B320&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -10169,7 +10137,7 @@
     <row r="321" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A321" s="4"/>
       <c r="B321" s="5"/>
-      <c r="C321" s="10" t="str">
+      <c r="C321" s="8" t="str">
         <f>IF(A321="",
     IF(B321&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -10191,7 +10159,7 @@
     <row r="322" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A322" s="4"/>
       <c r="B322" s="5"/>
-      <c r="C322" s="10" t="str">
+      <c r="C322" s="8" t="str">
         <f>IF(A322="",
     IF(B322&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -10213,7 +10181,7 @@
     <row r="323" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A323" s="4"/>
       <c r="B323" s="5"/>
-      <c r="C323" s="10" t="str">
+      <c r="C323" s="8" t="str">
         <f>IF(A323="",
     IF(B323&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -10235,7 +10203,7 @@
     <row r="324" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A324" s="4"/>
       <c r="B324" s="5"/>
-      <c r="C324" s="10" t="str">
+      <c r="C324" s="8" t="str">
         <f>IF(A324="",
     IF(B324&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -10257,7 +10225,7 @@
     <row r="325" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A325" s="4"/>
       <c r="B325" s="5"/>
-      <c r="C325" s="10" t="str">
+      <c r="C325" s="8" t="str">
         <f>IF(A325="",
     IF(B325&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -10279,7 +10247,7 @@
     <row r="326" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A326" s="4"/>
       <c r="B326" s="5"/>
-      <c r="C326" s="10" t="str">
+      <c r="C326" s="8" t="str">
         <f>IF(A326="",
     IF(B326&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -10301,7 +10269,7 @@
     <row r="327" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A327" s="4"/>
       <c r="B327" s="5"/>
-      <c r="C327" s="10" t="str">
+      <c r="C327" s="8" t="str">
         <f>IF(A327="",
     IF(B327&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -10323,7 +10291,7 @@
     <row r="328" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A328" s="4"/>
       <c r="B328" s="5"/>
-      <c r="C328" s="10" t="str">
+      <c r="C328" s="8" t="str">
         <f>IF(A328="",
     IF(B328&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -10345,7 +10313,7 @@
     <row r="329" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A329" s="4"/>
       <c r="B329" s="5"/>
-      <c r="C329" s="10" t="str">
+      <c r="C329" s="8" t="str">
         <f>IF(A329="",
     IF(B329&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -10367,7 +10335,7 @@
     <row r="330" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A330" s="4"/>
       <c r="B330" s="5"/>
-      <c r="C330" s="10" t="str">
+      <c r="C330" s="8" t="str">
         <f>IF(A330="",
     IF(B330&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -10389,7 +10357,7 @@
     <row r="331" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A331" s="4"/>
       <c r="B331" s="5"/>
-      <c r="C331" s="10" t="str">
+      <c r="C331" s="8" t="str">
         <f>IF(A331="",
     IF(B331&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -10411,7 +10379,7 @@
     <row r="332" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A332" s="4"/>
       <c r="B332" s="5"/>
-      <c r="C332" s="10" t="str">
+      <c r="C332" s="8" t="str">
         <f>IF(A332="",
     IF(B332&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -10433,7 +10401,7 @@
     <row r="333" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A333" s="4"/>
       <c r="B333" s="5"/>
-      <c r="C333" s="10" t="str">
+      <c r="C333" s="8" t="str">
         <f>IF(A333="",
     IF(B333&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -10455,7 +10423,7 @@
     <row r="334" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A334" s="4"/>
       <c r="B334" s="5"/>
-      <c r="C334" s="10" t="str">
+      <c r="C334" s="8" t="str">
         <f>IF(A334="",
     IF(B334&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -10477,7 +10445,7 @@
     <row r="335" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A335" s="4"/>
       <c r="B335" s="5"/>
-      <c r="C335" s="10" t="str">
+      <c r="C335" s="8" t="str">
         <f>IF(A335="",
     IF(B335&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -10499,7 +10467,7 @@
     <row r="336" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A336" s="4"/>
       <c r="B336" s="5"/>
-      <c r="C336" s="10" t="str">
+      <c r="C336" s="8" t="str">
         <f>IF(A336="",
     IF(B336&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -10521,7 +10489,7 @@
     <row r="337" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A337" s="4"/>
       <c r="B337" s="5"/>
-      <c r="C337" s="10" t="str">
+      <c r="C337" s="8" t="str">
         <f>IF(A337="",
     IF(B337&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -10543,7 +10511,7 @@
     <row r="338" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A338" s="4"/>
       <c r="B338" s="5"/>
-      <c r="C338" s="10" t="str">
+      <c r="C338" s="8" t="str">
         <f>IF(A338="",
     IF(B338&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -10565,7 +10533,7 @@
     <row r="339" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A339" s="4"/>
       <c r="B339" s="5"/>
-      <c r="C339" s="10" t="str">
+      <c r="C339" s="8" t="str">
         <f>IF(A339="",
     IF(B339&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -10587,7 +10555,7 @@
     <row r="340" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A340" s="4"/>
       <c r="B340" s="5"/>
-      <c r="C340" s="10" t="str">
+      <c r="C340" s="8" t="str">
         <f>IF(A340="",
     IF(B340&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -10609,7 +10577,7 @@
     <row r="341" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A341" s="4"/>
       <c r="B341" s="5"/>
-      <c r="C341" s="10" t="str">
+      <c r="C341" s="8" t="str">
         <f>IF(A341="",
     IF(B341&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -10631,7 +10599,7 @@
     <row r="342" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A342" s="4"/>
       <c r="B342" s="5"/>
-      <c r="C342" s="10" t="str">
+      <c r="C342" s="8" t="str">
         <f>IF(A342="",
     IF(B342&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -10653,7 +10621,7 @@
     <row r="343" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A343" s="4"/>
       <c r="B343" s="5"/>
-      <c r="C343" s="10" t="str">
+      <c r="C343" s="8" t="str">
         <f>IF(A343="",
     IF(B343&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -10675,7 +10643,7 @@
     <row r="344" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A344" s="4"/>
       <c r="B344" s="5"/>
-      <c r="C344" s="10" t="str">
+      <c r="C344" s="8" t="str">
         <f>IF(A344="",
     IF(B344&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -10697,7 +10665,7 @@
     <row r="345" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A345" s="4"/>
       <c r="B345" s="5"/>
-      <c r="C345" s="10" t="str">
+      <c r="C345" s="8" t="str">
         <f>IF(A345="",
     IF(B345&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -10719,7 +10687,7 @@
     <row r="346" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A346" s="4"/>
       <c r="B346" s="5"/>
-      <c r="C346" s="10" t="str">
+      <c r="C346" s="8" t="str">
         <f>IF(A346="",
     IF(B346&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -10741,7 +10709,7 @@
     <row r="347" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A347" s="4"/>
       <c r="B347" s="5"/>
-      <c r="C347" s="10" t="str">
+      <c r="C347" s="8" t="str">
         <f>IF(A347="",
     IF(B347&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -10763,7 +10731,7 @@
     <row r="348" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A348" s="4"/>
       <c r="B348" s="5"/>
-      <c r="C348" s="10" t="str">
+      <c r="C348" s="8" t="str">
         <f>IF(A348="",
     IF(B348&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -10785,7 +10753,7 @@
     <row r="349" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A349" s="4"/>
       <c r="B349" s="5"/>
-      <c r="C349" s="10" t="str">
+      <c r="C349" s="8" t="str">
         <f>IF(A349="",
     IF(B349&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -10807,7 +10775,7 @@
     <row r="350" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A350" s="4"/>
       <c r="B350" s="5"/>
-      <c r="C350" s="10" t="str">
+      <c r="C350" s="8" t="str">
         <f>IF(A350="",
     IF(B350&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -10829,7 +10797,7 @@
     <row r="351" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A351" s="4"/>
       <c r="B351" s="5"/>
-      <c r="C351" s="10" t="str">
+      <c r="C351" s="8" t="str">
         <f>IF(A351="",
     IF(B351&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -10851,7 +10819,7 @@
     <row r="352" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A352" s="4"/>
       <c r="B352" s="5"/>
-      <c r="C352" s="10" t="str">
+      <c r="C352" s="8" t="str">
         <f>IF(A352="",
     IF(B352&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -10873,7 +10841,7 @@
     <row r="353" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A353" s="4"/>
       <c r="B353" s="5"/>
-      <c r="C353" s="10" t="str">
+      <c r="C353" s="8" t="str">
         <f>IF(A353="",
     IF(B353&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -10895,7 +10863,7 @@
     <row r="354" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A354" s="4"/>
       <c r="B354" s="5"/>
-      <c r="C354" s="10" t="str">
+      <c r="C354" s="8" t="str">
         <f>IF(A354="",
     IF(B354&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -10917,7 +10885,7 @@
     <row r="355" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A355" s="4"/>
       <c r="B355" s="5"/>
-      <c r="C355" s="10" t="str">
+      <c r="C355" s="8" t="str">
         <f>IF(A355="",
     IF(B355&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -10939,7 +10907,7 @@
     <row r="356" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A356" s="4"/>
       <c r="B356" s="5"/>
-      <c r="C356" s="10" t="str">
+      <c r="C356" s="8" t="str">
         <f>IF(A356="",
     IF(B356&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -10961,7 +10929,7 @@
     <row r="357" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A357" s="4"/>
       <c r="B357" s="5"/>
-      <c r="C357" s="10" t="str">
+      <c r="C357" s="8" t="str">
         <f>IF(A357="",
     IF(B357&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -10983,7 +10951,7 @@
     <row r="358" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A358" s="4"/>
       <c r="B358" s="5"/>
-      <c r="C358" s="10" t="str">
+      <c r="C358" s="8" t="str">
         <f>IF(A358="",
     IF(B358&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -11005,7 +10973,7 @@
     <row r="359" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A359" s="4"/>
       <c r="B359" s="5"/>
-      <c r="C359" s="10" t="str">
+      <c r="C359" s="8" t="str">
         <f>IF(A359="",
     IF(B359&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -11027,7 +10995,7 @@
     <row r="360" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A360" s="4"/>
       <c r="B360" s="5"/>
-      <c r="C360" s="10" t="str">
+      <c r="C360" s="8" t="str">
         <f>IF(A360="",
     IF(B360&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -11049,7 +11017,7 @@
     <row r="361" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A361" s="4"/>
       <c r="B361" s="5"/>
-      <c r="C361" s="10" t="str">
+      <c r="C361" s="8" t="str">
         <f>IF(A361="",
     IF(B361&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -11071,7 +11039,7 @@
     <row r="362" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A362" s="4"/>
       <c r="B362" s="5"/>
-      <c r="C362" s="10" t="str">
+      <c r="C362" s="8" t="str">
         <f>IF(A362="",
     IF(B362&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -11093,7 +11061,7 @@
     <row r="363" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A363" s="4"/>
       <c r="B363" s="5"/>
-      <c r="C363" s="10" t="str">
+      <c r="C363" s="8" t="str">
         <f>IF(A363="",
     IF(B363&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -11115,7 +11083,7 @@
     <row r="364" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A364" s="4"/>
       <c r="B364" s="5"/>
-      <c r="C364" s="10" t="str">
+      <c r="C364" s="8" t="str">
         <f>IF(A364="",
     IF(B364&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -11137,7 +11105,7 @@
     <row r="365" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A365" s="4"/>
       <c r="B365" s="5"/>
-      <c r="C365" s="10" t="str">
+      <c r="C365" s="8" t="str">
         <f>IF(A365="",
     IF(B365&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -11159,7 +11127,7 @@
     <row r="366" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A366" s="4"/>
       <c r="B366" s="5"/>
-      <c r="C366" s="10" t="str">
+      <c r="C366" s="8" t="str">
         <f>IF(A366="",
     IF(B366&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -11181,7 +11149,7 @@
     <row r="367" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A367" s="4"/>
       <c r="B367" s="5"/>
-      <c r="C367" s="10" t="str">
+      <c r="C367" s="8" t="str">
         <f>IF(A367="",
     IF(B367&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -11203,7 +11171,7 @@
     <row r="368" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A368" s="4"/>
       <c r="B368" s="5"/>
-      <c r="C368" s="10" t="str">
+      <c r="C368" s="8" t="str">
         <f>IF(A368="",
     IF(B368&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -11225,7 +11193,7 @@
     <row r="369" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A369" s="4"/>
       <c r="B369" s="5"/>
-      <c r="C369" s="10" t="str">
+      <c r="C369" s="8" t="str">
         <f>IF(A369="",
     IF(B369&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -11247,7 +11215,7 @@
     <row r="370" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A370" s="4"/>
       <c r="B370" s="5"/>
-      <c r="C370" s="10" t="str">
+      <c r="C370" s="8" t="str">
         <f>IF(A370="",
     IF(B370&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -11269,7 +11237,7 @@
     <row r="371" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A371" s="4"/>
       <c r="B371" s="5"/>
-      <c r="C371" s="10" t="str">
+      <c r="C371" s="8" t="str">
         <f>IF(A371="",
     IF(B371&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -11291,7 +11259,7 @@
     <row r="372" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A372" s="4"/>
       <c r="B372" s="5"/>
-      <c r="C372" s="10" t="str">
+      <c r="C372" s="8" t="str">
         <f>IF(A372="",
     IF(B372&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -11313,7 +11281,7 @@
     <row r="373" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A373" s="4"/>
       <c r="B373" s="5"/>
-      <c r="C373" s="10" t="str">
+      <c r="C373" s="8" t="str">
         <f>IF(A373="",
     IF(B373&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -11335,7 +11303,7 @@
     <row r="374" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A374" s="4"/>
       <c r="B374" s="5"/>
-      <c r="C374" s="10" t="str">
+      <c r="C374" s="8" t="str">
         <f>IF(A374="",
     IF(B374&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -11357,7 +11325,7 @@
     <row r="375" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A375" s="4"/>
       <c r="B375" s="5"/>
-      <c r="C375" s="10" t="str">
+      <c r="C375" s="8" t="str">
         <f>IF(A375="",
     IF(B375&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -11379,7 +11347,7 @@
     <row r="376" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A376" s="4"/>
       <c r="B376" s="5"/>
-      <c r="C376" s="10" t="str">
+      <c r="C376" s="8" t="str">
         <f>IF(A376="",
     IF(B376&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -11401,7 +11369,7 @@
     <row r="377" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A377" s="4"/>
       <c r="B377" s="5"/>
-      <c r="C377" s="10" t="str">
+      <c r="C377" s="8" t="str">
         <f>IF(A377="",
     IF(B377&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -11423,7 +11391,7 @@
     <row r="378" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A378" s="4"/>
       <c r="B378" s="5"/>
-      <c r="C378" s="10" t="str">
+      <c r="C378" s="8" t="str">
         <f>IF(A378="",
     IF(B378&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -11445,7 +11413,7 @@
     <row r="379" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A379" s="4"/>
       <c r="B379" s="5"/>
-      <c r="C379" s="10" t="str">
+      <c r="C379" s="8" t="str">
         <f>IF(A379="",
     IF(B379&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -11467,7 +11435,7 @@
     <row r="380" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A380" s="4"/>
       <c r="B380" s="5"/>
-      <c r="C380" s="10" t="str">
+      <c r="C380" s="8" t="str">
         <f>IF(A380="",
     IF(B380&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -11489,7 +11457,7 @@
     <row r="381" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A381" s="4"/>
       <c r="B381" s="5"/>
-      <c r="C381" s="10" t="str">
+      <c r="C381" s="8" t="str">
         <f>IF(A381="",
     IF(B381&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -11511,7 +11479,7 @@
     <row r="382" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A382" s="4"/>
       <c r="B382" s="5"/>
-      <c r="C382" s="10" t="str">
+      <c r="C382" s="8" t="str">
         <f>IF(A382="",
     IF(B382&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -11533,7 +11501,7 @@
     <row r="383" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A383" s="4"/>
       <c r="B383" s="5"/>
-      <c r="C383" s="10" t="str">
+      <c r="C383" s="8" t="str">
         <f>IF(A383="",
     IF(B383&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -11555,7 +11523,7 @@
     <row r="384" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A384" s="4"/>
       <c r="B384" s="5"/>
-      <c r="C384" s="10" t="str">
+      <c r="C384" s="8" t="str">
         <f>IF(A384="",
     IF(B384&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -11577,7 +11545,7 @@
     <row r="385" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A385" s="4"/>
       <c r="B385" s="5"/>
-      <c r="C385" s="10" t="str">
+      <c r="C385" s="8" t="str">
         <f>IF(A385="",
     IF(B385&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -11599,7 +11567,7 @@
     <row r="386" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A386" s="4"/>
       <c r="B386" s="5"/>
-      <c r="C386" s="10" t="str">
+      <c r="C386" s="8" t="str">
         <f>IF(A386="",
     IF(B386&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -11621,7 +11589,7 @@
     <row r="387" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A387" s="4"/>
       <c r="B387" s="5"/>
-      <c r="C387" s="10" t="str">
+      <c r="C387" s="8" t="str">
         <f>IF(A387="",
     IF(B387&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -11643,7 +11611,7 @@
     <row r="388" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A388" s="4"/>
       <c r="B388" s="5"/>
-      <c r="C388" s="10" t="str">
+      <c r="C388" s="8" t="str">
         <f>IF(A388="",
     IF(B388&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -11665,7 +11633,7 @@
     <row r="389" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A389" s="4"/>
       <c r="B389" s="5"/>
-      <c r="C389" s="10" t="str">
+      <c r="C389" s="8" t="str">
         <f>IF(A389="",
     IF(B389&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -11687,7 +11655,7 @@
     <row r="390" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A390" s="4"/>
       <c r="B390" s="5"/>
-      <c r="C390" s="10" t="str">
+      <c r="C390" s="8" t="str">
         <f>IF(A390="",
     IF(B390&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -11709,7 +11677,7 @@
     <row r="391" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A391" s="4"/>
       <c r="B391" s="5"/>
-      <c r="C391" s="10" t="str">
+      <c r="C391" s="8" t="str">
         <f>IF(A391="",
     IF(B391&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -11731,7 +11699,7 @@
     <row r="392" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A392" s="4"/>
       <c r="B392" s="5"/>
-      <c r="C392" s="10" t="str">
+      <c r="C392" s="8" t="str">
         <f>IF(A392="",
     IF(B392&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -11753,7 +11721,7 @@
     <row r="393" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A393" s="4"/>
       <c r="B393" s="5"/>
-      <c r="C393" s="10" t="str">
+      <c r="C393" s="8" t="str">
         <f>IF(A393="",
     IF(B393&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -11775,7 +11743,7 @@
     <row r="394" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A394" s="4"/>
       <c r="B394" s="5"/>
-      <c r="C394" s="10" t="str">
+      <c r="C394" s="8" t="str">
         <f>IF(A394="",
     IF(B394&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -11797,7 +11765,7 @@
     <row r="395" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A395" s="4"/>
       <c r="B395" s="5"/>
-      <c r="C395" s="10" t="str">
+      <c r="C395" s="8" t="str">
         <f>IF(A395="",
     IF(B395&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -11819,7 +11787,7 @@
     <row r="396" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A396" s="4"/>
       <c r="B396" s="5"/>
-      <c r="C396" s="10" t="str">
+      <c r="C396" s="8" t="str">
         <f>IF(A396="",
     IF(B396&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -11841,7 +11809,7 @@
     <row r="397" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A397" s="4"/>
       <c r="B397" s="5"/>
-      <c r="C397" s="10" t="str">
+      <c r="C397" s="8" t="str">
         <f>IF(A397="",
     IF(B397&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -11863,7 +11831,7 @@
     <row r="398" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A398" s="4"/>
       <c r="B398" s="5"/>
-      <c r="C398" s="10" t="str">
+      <c r="C398" s="8" t="str">
         <f>IF(A398="",
     IF(B398&lt;&gt;"", "You need to select a GPCR.", ""),
     IF(SUM(
@@ -11882,44 +11850,22 @@
         <v/>
       </c>
     </row>
-    <row r="399" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A399" s="6"/>
-      <c r="B399" s="7"/>
-      <c r="C399" s="10" t="str">
-        <f>IF(A399="",
-    IF(B399&lt;&gt;"", "You need to select a GPCR.", ""),
-    IF(SUM(
-        COUNTIF(ReceptorData[GPCRs
-(UniProt)], A399),
-        COUNTIF(ReceptorData[GPCRs
-(Gene name)], A399)
-    )=0,  "Invalid GPCR (Try to take a look at the 'GPCR lookup table' Sheet).",
-        IF(B399="", "You need to add a number in column B.",
-            IF(NOT(ISNUMBER(B399)), "Column B needs to be a number.",
-                "Correctly formatted."
-            )
-        )
-    )
-)</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="C2:C399">
-    <cfRule type="expression" dxfId="5" priority="1">
+  <conditionalFormatting sqref="C2:C398">
+    <cfRule type="expression" dxfId="4" priority="1">
       <formula>C2="You need to select a GPCR."</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="2">
+    <cfRule type="expression" dxfId="3" priority="2">
       <formula>C2="Invalid GPCR (Try to take a look at the 'GPCR lookup table' Sheet)."</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="3">
+    <cfRule type="expression" dxfId="2" priority="3">
       <formula>C2="Column B needs to be a number."</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="4">
+    <cfRule type="expression" dxfId="1" priority="4">
       <formula>C2="You need to add a number in column B."</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="5">
+    <cfRule type="expression" dxfId="0" priority="5">
       <formula>OR(C2="Will be processed.", C2="Correctly formatted.")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11944,10 +11890,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="10" t="s">
         <v>504</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="10" t="s">
         <v>505</v>
       </c>
       <c r="C1" s="2" t="s">
